--- a/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
+++ b/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
@@ -5,29 +5,30 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\SALTA 1167\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE999FA-268C-484D-B421-4C13AB75868B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEA045A-A6FC-4553-887B-90047F09610C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="EDESUR" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId3"/>
+    <sheet name="EDESUR" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">EDESUR!$B$3:$J$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$93</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="150">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -325,144 +326,162 @@
     <t>Martina Belen Carbone</t>
   </si>
   <si>
-    <t>¡IMPORTANTE!                                                                                                                                                                                                                                                                                                                                                                    Estimados convivientes:
+    <t>Gastos A</t>
+  </si>
+  <si>
+    <t>Gastos B</t>
+  </si>
+  <si>
+    <t>TOTAL GASTOS A</t>
+  </si>
+  <si>
+    <t>GASTOS B:</t>
+  </si>
+  <si>
+    <t>TOTAL GASTOS B:</t>
+  </si>
+  <si>
+    <t>PREVISION GASTOS B</t>
+  </si>
+  <si>
+    <t>PREVISION GASTOS A</t>
+  </si>
+  <si>
+    <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</t>
+  </si>
+  <si>
+    <t>Egresos del mes gastos A</t>
+  </si>
+  <si>
+    <t>Egresos del mes gastos B</t>
+  </si>
+  <si>
+    <t>GASTOS A - UNIDADES FUNCIONALES:</t>
+  </si>
+  <si>
+    <t>GASTOS A + PREVISION (A) :</t>
+  </si>
+  <si>
+    <t>GASTOS A SIN PREVISION:</t>
+  </si>
+  <si>
+    <t>GASTOS B SIN PREVISION:</t>
+  </si>
+  <si>
+    <t>GASTOS B CON PREVISION (B):</t>
+  </si>
+  <si>
+    <t>SALDO CAJA A</t>
+  </si>
+  <si>
+    <t>SALDO CAJA B</t>
+  </si>
+  <si>
+    <t>Ingresos cobros tipo A</t>
+  </si>
+  <si>
+    <t>Ingresos cobros tipo B</t>
+  </si>
+  <si>
+    <t>CAJA A</t>
+  </si>
+  <si>
+    <t>CAJA B</t>
+  </si>
+  <si>
+    <t>Full Clean - Servicio de limpieza</t>
+  </si>
+  <si>
+    <t>Gastos bancarios</t>
+  </si>
+  <si>
+    <t>Lema - Ascensores - Servicio de mantenimiento - Se abona a mes vencido</t>
+  </si>
+  <si>
+    <t>Alejo Moreno</t>
+  </si>
+  <si>
+    <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
+  </si>
+  <si>
+    <t>Totales</t>
+  </si>
+  <si>
+    <t>Bonificado x EDESUR Noviembre</t>
+  </si>
+  <si>
+    <t>Sr. Hector Piletero</t>
+  </si>
+  <si>
+    <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
+  </si>
+  <si>
+    <t>VTO 16/02</t>
+  </si>
+  <si>
+    <t>PERÍODO: ENERO</t>
+  </si>
+  <si>
+    <t>Transf 08/01</t>
+  </si>
+  <si>
+    <t>Consumos PARTICULARES</t>
+  </si>
+  <si>
+    <t>Consumos GENERALES</t>
+  </si>
+  <si>
+    <t>Bonificado x EDESUR</t>
+  </si>
+  <si>
+    <t>Consumo Kw</t>
+  </si>
+  <si>
+    <t>% Consumido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo x Dep </t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>Cons Esp Com</t>
+  </si>
+  <si>
+    <t>Cons Coch</t>
+  </si>
+  <si>
+    <t>TOTAL FACT EDESUR</t>
+  </si>
+  <si>
+    <t>Bonificacion apertura de cuenta bancaria</t>
+  </si>
+  <si>
+    <t>Debito 06/01</t>
+  </si>
+  <si>
+    <t>Transf 07/01</t>
+  </si>
+  <si>
+    <t>Transf 26/01</t>
+  </si>
+  <si>
+    <t>Ef.</t>
+  </si>
+  <si>
+    <t>Subidos en en3r0</t>
+  </si>
+  <si>
+    <t>REITERAMOS QUE LOS DATOS DE LA CUENTA EN DONDE DEBEN ABONAR LAS EXPENSAS SON: CONSORCIO DE PROPIETARIOS EDIFICIO CALLE SALTA 1167/1169  - C DE P SALTA 1167 1169 LANUS - CTA CTE $   039 - 22273/6   CBU: 0720039720000002227368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                           Estimados convivientes:
 Les solicitamos, por favor, que al momento de realizar el pago respeten los centavos que figuran en el monto indicado, ya que estos nos permiten identificar correctamente los pagos y las unidades funcionales, reduciendo así el margen de error.
 Muchas gracias por su colaboración.</t>
   </si>
   <si>
-    <t>Gastos A</t>
-  </si>
-  <si>
-    <t>Gastos B</t>
-  </si>
-  <si>
-    <t>TOTAL GASTOS A</t>
-  </si>
-  <si>
-    <t>GASTOS B:</t>
-  </si>
-  <si>
-    <t>TOTAL GASTOS B:</t>
-  </si>
-  <si>
-    <t>PREVISION GASTOS B</t>
-  </si>
-  <si>
-    <t>PREVISION GASTOS A</t>
-  </si>
-  <si>
-    <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</t>
-  </si>
-  <si>
-    <t>Egresos del mes gastos A</t>
-  </si>
-  <si>
-    <t>Egresos del mes gastos B</t>
-  </si>
-  <si>
-    <t>GASTOS A - UNIDADES FUNCIONALES:</t>
-  </si>
-  <si>
-    <t>GASTOS A + PREVISION (A) :</t>
-  </si>
-  <si>
-    <t>GASTOS A SIN PREVISION:</t>
-  </si>
-  <si>
-    <t>GASTOS B SIN PREVISION:</t>
-  </si>
-  <si>
-    <t>GASTOS B CON PREVISION (B):</t>
-  </si>
-  <si>
-    <t>SALDO CAJA A</t>
-  </si>
-  <si>
-    <t>SALDO CAJA B</t>
-  </si>
-  <si>
-    <t>Ingresos cobros tipo A</t>
-  </si>
-  <si>
-    <t>Ingresos cobros tipo B</t>
-  </si>
-  <si>
-    <t>CAJA A</t>
-  </si>
-  <si>
-    <t>CAJA B</t>
-  </si>
-  <si>
-    <t>Full Clean - Servicio de limpieza</t>
-  </si>
-  <si>
-    <t>Indugar SRL - Compra de pinturas trabajo en medianera</t>
-  </si>
-  <si>
-    <t>Gastos bancarios</t>
-  </si>
-  <si>
-    <t>Bonificacion apertura de cuenta bancaria (pago de servicios)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chavez Pablo - Impermeabilizacion de medianera </t>
-  </si>
-  <si>
-    <t>Transf 16/12</t>
-  </si>
-  <si>
-    <t>Transf 22/12</t>
-  </si>
-  <si>
-    <t>Transf 02/12</t>
-  </si>
-  <si>
-    <t>Debito 09/12</t>
-  </si>
-  <si>
-    <t>Lema - Ascensores - Servicio de mantenimiento - Se abona a mes vencido</t>
-  </si>
-  <si>
-    <t>Pintureria Gianonni - Bricol para ceramicos</t>
-  </si>
-  <si>
-    <t>Sr.  Pucheta</t>
-  </si>
-  <si>
-    <t>QUIENES ESTAN MARCADOS DE COLOR VERDE NO HAN ABONADO A LA CUENTA BANCARIA CORRESPONDIENTE. REITERAMOS QUE LOS DATOS DE LA CUENTA EN DONDE DEBEN ABONAR LAS EXPENSAS SON: CONSORCIO DE PROPIETARIOS EDIFICIO CALLE SALTA 1167/1169  - C DE P SALTA 1167 1169 LANUS - CTA CTE $   039 - 22273/6                                                                                                                 CBU: 0720039720000002227368</t>
-  </si>
-  <si>
-    <t>Alejo Moreno</t>
-  </si>
-  <si>
-    <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
-  </si>
-  <si>
-    <t>Totales</t>
-  </si>
-  <si>
-    <t>Bonificado x EDESUR Noviembre</t>
-  </si>
-  <si>
-    <t>Sr. Hector Piletero</t>
-  </si>
-  <si>
-    <t>Transf 30/12</t>
-  </si>
-  <si>
-    <t>Transf 29/12</t>
-  </si>
-  <si>
-    <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
-  </si>
-  <si>
-    <t>VTO 16/02</t>
-  </si>
-  <si>
-    <t>PERÍODO: ENERO</t>
-  </si>
-  <si>
-    <t>Transf 08/01</t>
+    <t>Transf 29/01</t>
   </si>
 </sst>
 </file>
@@ -480,7 +499,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -674,6 +693,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -749,7 +783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1049,21 +1083,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -1114,12 +1133,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1200,15 +1220,14 @@
     <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1216,9 +1235,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1254,10 +1270,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1365,20 +1381,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="11" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="11" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1421,9 +1423,8 @@
     <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1440,6 +1441,77 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1449,7 +1521,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1510,31 +1582,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1554,28 +1626,33 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1935,22 +2012,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M97"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
         <v>78</v>
@@ -1959,7 +2036,7 @@
       <c r="D1" s="51"/>
       <c r="E1" s="52"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="53" t="s">
         <v>14</v>
@@ -1968,32 +2045,32 @@
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="218" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="219"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="70" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="53" t="s">
@@ -2001,7 +2078,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
@@ -2012,764 +2089,717 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="201" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="201"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="201"/>
-      <c r="C9" s="201"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="201"/>
-      <c r="C10" s="201"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="200" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="200"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="200"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="200"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="221" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="221"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="220" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="220"/>
+      <c r="C13" s="220"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="220"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="220"/>
+      <c r="B14" s="220"/>
+      <c r="C14" s="220"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="220"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="220"/>
+      <c r="B15" s="220"/>
+      <c r="C15" s="220"/>
+      <c r="D15" s="220"/>
+      <c r="E15" s="220"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="220"/>
+      <c r="B16" s="220"/>
+      <c r="C16" s="220"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>81</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="104"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="196" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="197"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="102"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="216" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="217"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="240">
+      <c r="D22" s="118">
         <v>465000.72</v>
       </c>
-      <c r="E22" s="113" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" s="93"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="196"/>
-      <c r="B23" s="197"/>
+      <c r="E22" s="111" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="91"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="216"/>
+      <c r="B23" s="217"/>
       <c r="C23" s="39"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="113"/>
-      <c r="H23" s="93"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D23" s="118"/>
+      <c r="E23" s="111"/>
+      <c r="H23" s="91"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="134">
+      <c r="D24" s="119"/>
+      <c r="E24" s="132">
         <f>SUM(D22:D23)</f>
         <v>465000.72</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="133"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="197"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="131"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="216" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="217"/>
       <c r="C26" s="41"/>
-      <c r="D26" s="195">
-        <v>74591</v>
-      </c>
-      <c r="E26" s="106" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D26" s="182">
+        <v>74584</v>
+      </c>
+      <c r="E26" s="104" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="105">
+      <c r="D27" s="119"/>
+      <c r="E27" s="103">
         <f>SUM(D26:D26)</f>
-        <v>74591</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>74584</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="108"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="109"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="106"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="121"/>
+      <c r="E28" s="107"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="114">
-        <v>0</v>
-      </c>
-      <c r="E29" s="113"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="112">
+        <v>0</v>
+      </c>
+      <c r="E29" s="111"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="238">
+      <c r="D30" s="112">
         <v>5760.77</v>
       </c>
-      <c r="E30" s="113" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E30" s="111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="130"/>
+      <c r="B31" s="128"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="238">
+      <c r="D31" s="112">
         <v>275296.83</v>
       </c>
-      <c r="E31" s="113" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="202" t="s">
+      <c r="E31" s="111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="222" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="203"/>
+      <c r="B32" s="223"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="238">
-        <v>358176.46</v>
-      </c>
-      <c r="E32" s="113" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="116" t="s">
+      <c r="D32" s="112">
+        <v>388176.46</v>
+      </c>
+      <c r="E32" s="111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="112"/>
+      <c r="B33" s="110"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="114">
-        <v>21236.33</v>
-      </c>
-      <c r="E33" s="113" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="112">
+        <v>22064.59</v>
+      </c>
+      <c r="E33" s="111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="107">
+      <c r="D34" s="122"/>
+      <c r="E34" s="105">
         <f>SUM(D29:D33)</f>
-        <v>660470.39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>691298.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="110"/>
-    </row>
-    <row r="36" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="196" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="197"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="108"/>
+    </row>
+    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="216" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="217"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="114"/>
-      <c r="E36" s="115"/>
-    </row>
-    <row r="37" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="131" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="132"/>
+      <c r="D36" s="112">
+        <v>75000</v>
+      </c>
+      <c r="E36" s="113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="129" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="130"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="239">
-        <v>82600</v>
-      </c>
-      <c r="E37" s="115" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="196" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" s="197"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="78">
-        <v>1537000</v>
-      </c>
-      <c r="E38" s="115" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="196" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="197"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="78">
-        <v>90000</v>
-      </c>
-      <c r="E39" s="115" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="196" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="197"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="78">
-        <v>42370</v>
-      </c>
-      <c r="E40" s="115" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="196" t="s">
-        <v>130</v>
-      </c>
-      <c r="B41" s="197"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="78">
-        <v>24884.21</v>
-      </c>
-      <c r="E41" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D37" s="76">
+        <v>103200</v>
+      </c>
+      <c r="E37" s="113" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="103">
+        <f>SUM(D36:D37)</f>
+        <v>178200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="102"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="216" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="217"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="118">
+        <v>149700</v>
+      </c>
+      <c r="E40" s="135" t="s">
+        <v>149</v>
+      </c>
+      <c r="G40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="129"/>
+      <c r="B41" s="130"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="135"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="132">
+        <f>SUM(D40:D41)</f>
+        <v>149700</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="49"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="103"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="109"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="112">
+        <v>20348</v>
+      </c>
+      <c r="E45" s="29"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="133">
+        <f>SUM(D44:D45)</f>
+        <v>20348</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="79"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="134"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="31"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="84">
+        <f>(SUM(E21:E48))</f>
+        <v>1579131.37</v>
+      </c>
+      <c r="F50" s="101"/>
+      <c r="G50" s="31"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="H52" s="123"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="86"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="75"/>
+      <c r="B54" s="110"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="74"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="226"/>
+      <c r="B55" s="226"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="74"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="75"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="76"/>
+      <c r="E57" s="74"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="36"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42">
+        <f>SUM(D54:D57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="215"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="8"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="50">
+        <f>E58+E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="72">
+        <f>E50</f>
+        <v>1579131.37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="72">
+        <f>E50-E48</f>
+        <v>1579131.37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" s="72">
+        <f>E63-E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="72">
+        <f>E63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="27"/>
+    </row>
+    <row r="71" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B71" s="148">
+        <v>-991192.32999999973</v>
+      </c>
+      <c r="C71" s="27"/>
+      <c r="D71" s="34"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B72" s="98">
+        <f>-B66</f>
+        <v>-1579131.37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B73" s="98">
+        <f>B92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="99">
+        <f>PRORRATEO!G36-B82</f>
+        <v>1869474.7999999996</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" s="99"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" s="124"/>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" s="97">
+        <f>SUM(B71:C76)</f>
+        <v>-700848.90000000014</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="94"/>
+      <c r="B78" s="94"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="30"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="93" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="148">
+        <v>2000000</v>
+      </c>
+      <c r="D79" s="30"/>
+      <c r="E79" s="31"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="98">
+        <f>-B67</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="31"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="98">
+        <f>B100</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="31">
+        <f>B84+B77</f>
+        <v>1299151.0999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B82" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" s="124"/>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="96" t="s">
+        <v>118</v>
+      </c>
+      <c r="B84" s="97">
+        <f>SUM(B79:C83)</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="94"/>
+      <c r="B85" s="94"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="94"/>
+      <c r="B86" s="94"/>
+    </row>
+    <row r="87" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="225" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="225"/>
+      <c r="C88" s="225"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="225"/>
+      <c r="B89" s="225"/>
+      <c r="C89" s="225"/>
+    </row>
+    <row r="90" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="88"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26">
+        <v>40000</v>
+      </c>
+      <c r="E90" s="101"/>
+    </row>
+    <row r="91" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="88"/>
+      <c r="B91" s="90"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="101"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="105">
-        <f>SUM(D36:D41)</f>
-        <v>1776854.21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="104"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="197"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="120">
-        <v>140000</v>
-      </c>
-      <c r="E44" s="137"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="131"/>
-      <c r="B45" s="132"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="137"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="121"/>
-      <c r="E46" s="134">
-        <f>SUM(D44:D45)</f>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="49"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="105"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="114"/>
-      <c r="E48" s="111"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="114">
-        <f>40662.21-311.85-1485-4686.04-151.2-720-450+720+151.2+540</f>
-        <v>34269.32</v>
-      </c>
-      <c r="E49" s="29"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="135">
-        <f>SUM(D48:D49)</f>
-        <v>34269.32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="81"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="136"/>
-    </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="84"/>
-      <c r="F53" s="31"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="86">
-        <f>(SUM(E21:E52))</f>
-        <v>3151185.6399999997</v>
-      </c>
-      <c r="F54" s="103"/>
-      <c r="G54" s="31"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
-      <c r="H56" s="125"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="88"/>
-    </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="77"/>
-      <c r="B58" s="112"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="76"/>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="206"/>
-      <c r="B59" s="206"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="114"/>
-      <c r="E59" s="76"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="77"/>
-      <c r="B61" s="79"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="76"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42">
-        <f>SUM(D58:D61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="74"/>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="50">
-        <f>E62+E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="B69" s="73">
-        <f>E54</f>
-        <v>3151185.6399999997</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="B70" s="73">
-        <f>E54-E52</f>
-        <v>3151185.6399999997</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="B71" s="73">
-        <f>E67-E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="B72" s="73">
-        <f>E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="27"/>
-    </row>
-    <row r="75" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="95" t="s">
-        <v>114</v>
-      </c>
-      <c r="B75" s="150">
-        <v>115565.9499999996</v>
-      </c>
-      <c r="C75" s="27"/>
-      <c r="D75" s="34"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="B76" s="100">
-        <f>-B70</f>
-        <v>-3151185.6399999997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B77" s="100">
-        <f>B96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="B78" s="101">
-        <f>PRORRATEO!G36-B86</f>
-        <v>1986908.7200000002</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="B79" s="101">
-        <f>102287.66+2747.19</f>
-        <v>105034.85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="102" t="s">
-        <v>25</v>
-      </c>
-      <c r="B80" s="126"/>
-    </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="98" t="s">
-        <v>118</v>
-      </c>
-      <c r="B81" s="99">
-        <f>SUM(B75:C80)</f>
-        <v>-943676.11999999976</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="96"/>
-      <c r="B82" s="96"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="30"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="95" t="s">
-        <v>115</v>
-      </c>
-      <c r="B83" s="150">
-        <v>2000000</v>
-      </c>
-      <c r="D83" s="30"/>
-      <c r="E83" s="31"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="B84" s="100">
-        <f>-B71</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="31"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B85" s="100">
-        <f>B104</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="31"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="B86" s="101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="102" t="s">
-        <v>25</v>
-      </c>
-      <c r="B87" s="126"/>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="B88" s="99">
-        <f>SUM(B83:C87)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="96"/>
-      <c r="B89" s="96"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="96"/>
-      <c r="B90" s="96"/>
-    </row>
-    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="205" t="s">
-        <v>19</v>
-      </c>
-      <c r="B92" s="205"/>
-      <c r="C92" s="205"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="205"/>
-      <c r="B93" s="205"/>
-      <c r="C93" s="205"/>
-    </row>
-    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="90"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26">
-        <v>40000</v>
-      </c>
-      <c r="E94" s="103"/>
-    </row>
-    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="90"/>
-      <c r="B95" s="92"/>
-      <c r="C95" s="89"/>
-      <c r="D95" s="103"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="91">
-        <f>SUM(B94:B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="33"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M97" s="6"/>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="204"/>
-      <c r="B98" s="204"/>
-      <c r="C98" s="204"/>
-      <c r="D98" s="204"/>
-      <c r="E98" s="204"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="204"/>
-      <c r="B99" s="204"/>
-      <c r="C99" s="204"/>
-      <c r="D99" s="204"/>
-      <c r="E99" s="204"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="204"/>
-      <c r="B100" s="204"/>
-      <c r="C100" s="204"/>
-      <c r="D100" s="204"/>
-      <c r="E100" s="204"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="204"/>
-      <c r="B101" s="204"/>
-      <c r="C101" s="204"/>
-      <c r="D101" s="204"/>
-      <c r="E101" s="204"/>
+      <c r="B92" s="89">
+        <f>SUM(B90:B91)</f>
+        <v>0</v>
+      </c>
+      <c r="C92" s="33"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M93" s="6"/>
+    </row>
+    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="224"/>
+      <c r="B94" s="224"/>
+      <c r="C94" s="224"/>
+      <c r="D94" s="224"/>
+      <c r="E94" s="224"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="224"/>
+      <c r="B95" s="224"/>
+      <c r="C95" s="224"/>
+      <c r="D95" s="224"/>
+      <c r="E95" s="224"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="224"/>
+      <c r="B96" s="224"/>
+      <c r="C96" s="224"/>
+      <c r="D96" s="224"/>
+      <c r="E96" s="224"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="224"/>
+      <c r="B97" s="224"/>
+      <c r="C97" s="224"/>
+      <c r="D97" s="224"/>
+      <c r="E97" s="224"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A98:E101"/>
-    <mergeCell ref="A92:C93"/>
-    <mergeCell ref="A59:B59"/>
+  <mergeCells count="12">
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A94:E97"/>
+    <mergeCell ref="A88:C89"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
@@ -2777,7 +2807,6 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2787,284 +2816,299 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="161"/>
-      <c r="B1" s="162"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
-      <c r="M1" s="207"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="164"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="165"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169">
-        <v>0</v>
-      </c>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="168" t="s">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="149"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="152"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="171">
+      <c r="F2" s="156"/>
+      <c r="G2" s="157">
+        <v>0</v>
+      </c>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="156" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="159">
         <v>2000000</v>
       </c>
-      <c r="M2" s="172"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="174"/>
-      <c r="P2" s="20"/>
-    </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="165"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="167"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="167"/>
-      <c r="L3" s="167"/>
-      <c r="M3" s="172"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="20"/>
-    </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="219" t="s">
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="153"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="20"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="239" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="240"/>
+      <c r="C4" s="240"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
+      <c r="M4" s="240"/>
+      <c r="N4" s="240"/>
+      <c r="O4" s="240"/>
+      <c r="P4" s="241"/>
+      <c r="Q4" s="20"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="242"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
+      <c r="O5" s="243"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="242"/>
+      <c r="B6" s="243"/>
+      <c r="C6" s="243"/>
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="244"/>
+      <c r="Q6" s="20"/>
+    </row>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="242"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="243"/>
+      <c r="O7" s="243"/>
+      <c r="P7" s="244"/>
+      <c r="Q7" s="20"/>
+    </row>
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="245"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="246"/>
+      <c r="D8" s="246"/>
+      <c r="E8" s="246"/>
+      <c r="F8" s="246"/>
+      <c r="G8" s="246"/>
+      <c r="H8" s="246"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="246"/>
+      <c r="K8" s="246"/>
+      <c r="L8" s="246"/>
+      <c r="M8" s="246"/>
+      <c r="N8" s="246"/>
+      <c r="O8" s="246"/>
+      <c r="P8" s="247"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="250" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="251"/>
+      <c r="C9" s="251"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
+      <c r="M9" s="251"/>
+      <c r="N9" s="251"/>
+      <c r="O9" s="251"/>
+      <c r="P9" s="251"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="252" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="252"/>
+      <c r="C10" s="252"/>
+      <c r="D10" s="252"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="252"/>
+      <c r="L10" s="252"/>
+      <c r="M10" s="252"/>
+      <c r="N10" s="252"/>
+      <c r="O10" s="252"/>
+      <c r="P10" s="252"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="232" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="125"/>
+      <c r="C11" s="232" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="232" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="232" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="228" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="232" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="234" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="228" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="228" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="228" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="20"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="223"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="223"/>
-      <c r="O5" s="224"/>
-      <c r="P5" s="20"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="222"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="223"/>
-      <c r="O6" s="224"/>
-      <c r="P6" s="20"/>
-    </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="224"/>
-      <c r="P7" s="20"/>
-    </row>
-    <row r="8" spans="1:16" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="225"/>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="226"/>
-      <c r="O8" s="227"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="230" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="231"/>
-      <c r="H9" s="231"/>
-      <c r="I9" s="231"/>
-      <c r="J9" s="231"/>
-      <c r="K9" s="231"/>
-      <c r="L9" s="231"/>
-      <c r="M9" s="231"/>
-      <c r="N9" s="231"/>
-      <c r="O9" s="231"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="232" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="232"/>
-      <c r="C10" s="232"/>
-      <c r="D10" s="232"/>
-      <c r="E10" s="232"/>
-      <c r="F10" s="232"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="232"/>
-      <c r="I10" s="232"/>
-      <c r="J10" s="232"/>
-      <c r="K10" s="232"/>
-      <c r="L10" s="232"/>
-      <c r="M10" s="232"/>
-      <c r="N10" s="232"/>
-      <c r="O10" s="232"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="212" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="127"/>
-      <c r="C11" s="212" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="212" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="212" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="208" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="212" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="214" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="208" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="208" t="s">
+      <c r="L11" s="237" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" s="228" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="208" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="217" t="s">
-        <v>100</v>
-      </c>
-      <c r="M11" s="45" t="s">
+      <c r="N11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="210" t="s">
+      <c r="O11" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="228" t="s">
+      <c r="P11" s="248" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="213"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="213"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="209"/>
-      <c r="G12" s="213"/>
-      <c r="H12" s="215"/>
-      <c r="I12" s="209"/>
-      <c r="J12" s="216"/>
-      <c r="K12" s="209"/>
-      <c r="L12" s="218"/>
-      <c r="M12" s="43" t="str">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="233"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="229"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="229"/>
+      <c r="L12" s="238"/>
+      <c r="M12" s="229"/>
+      <c r="N12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="N12" s="211"/>
-      <c r="O12" s="229"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="231"/>
+      <c r="P12" s="249"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>1</v>
       </c>
@@ -3079,49 +3123,53 @@
         <v>12</v>
       </c>
       <c r="F13" s="56">
-        <v>232082.01</v>
+        <v>240000.01</v>
       </c>
       <c r="G13" s="57">
-        <f>256082.01-G29-G30</f>
-        <v>232081.66</v>
+        <f>264000-G29-G30</f>
+        <v>239999.65</v>
       </c>
       <c r="H13" s="58">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>0.35000000000582077</v>
+        <v>0.36000000001513399</v>
       </c>
       <c r="I13" s="58">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>1.0500000000174623E-2</v>
+        <v>1.0800000000454019E-2</v>
       </c>
       <c r="J13" s="59">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="K13" s="117">
+      <c r="K13" s="115">
         <f>L$2*E13/100</f>
         <v>240000</v>
       </c>
-      <c r="L13" s="117">
+      <c r="L13" s="115">
         <f>G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="M13" s="60">
-        <f>ROUND(SUM(H13:L13),0) + P13</f>
+      <c r="M13" s="213">
+        <f>Hoja1!O4</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="211">
+        <f>ROUND(SUM(H13:M13),0) + Q13</f>
         <v>240000.01</v>
       </c>
-      <c r="N13" s="61">
-        <f>ROUND(M13*6% + M13,0) + P13</f>
+      <c r="O13" s="60">
+        <f>ROUND(N13*6% + N13,0) + Q13</f>
         <v>254400.01</v>
       </c>
-      <c r="O13" s="62">
-        <f>ROUND(M13*3%,0) + M13</f>
+      <c r="P13" s="61">
+        <f>ROUND(N13*3%,0) + N13</f>
         <v>247200.01</v>
       </c>
-      <c r="P13" s="31">
+      <c r="Q13" s="31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>2</v>
       </c>
@@ -3139,47 +3187,51 @@
         <v>132000.01999999999</v>
       </c>
       <c r="G14" s="57">
-        <f>F14</f>
-        <v>132000.01999999999</v>
+        <f>130000</f>
+        <v>130000</v>
       </c>
       <c r="H14" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2000.0199999999895</v>
       </c>
       <c r="I14" s="58">
         <f t="shared" ref="I14:I35" si="1">IF(H14&gt;0,H14*3%,0)</f>
-        <v>0</v>
+        <v>60.000599999999686</v>
       </c>
       <c r="J14" s="59">
         <f>EDESUR!I6</f>
         <v>0</v>
       </c>
-      <c r="K14" s="117">
+      <c r="K14" s="115">
         <f t="shared" ref="K14:K35" si="2">L$2*E14/100</f>
         <v>132000</v>
       </c>
-      <c r="L14" s="117">
+      <c r="L14" s="115">
         <f t="shared" ref="L14:L35" si="3">G$2*E14/100</f>
         <v>0</v>
       </c>
-      <c r="M14" s="60">
-        <f t="shared" ref="M14:M35" si="4">ROUND(SUM(H14:L14),0) + P14</f>
-        <v>132000.01999999999</v>
-      </c>
-      <c r="N14" s="61">
-        <f t="shared" ref="N14:N30" si="5">ROUND(M14*6% + M14,0) + P14</f>
-        <v>139920.01999999999</v>
-      </c>
-      <c r="O14" s="62">
-        <f t="shared" ref="O14:O35" si="6">ROUND(M14*3%,0) + M14</f>
-        <v>135960.01999999999</v>
-      </c>
-      <c r="P14" s="31">
-        <f>P13+0.01</f>
+      <c r="M14" s="213">
+        <f>Hoja1!O5</f>
+        <v>9105.9822987988518</v>
+      </c>
+      <c r="N14" s="211">
+        <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
+        <v>143166.01999999999</v>
+      </c>
+      <c r="O14" s="60">
+        <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
+        <v>151756.01999999999</v>
+      </c>
+      <c r="P14" s="61">
+        <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
+        <v>147461.01999999999</v>
+      </c>
+      <c r="Q14" s="31">
+        <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>3</v>
       </c>
@@ -3214,32 +3266,36 @@
         <f>EDESUR!I7</f>
         <v>0</v>
       </c>
-      <c r="K15" s="117">
+      <c r="K15" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L15" s="117">
+      <c r="L15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="60">
+      <c r="M15" s="213">
+        <f>Hoja1!O6</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="211">
         <f t="shared" si="4"/>
         <v>108000.03</v>
       </c>
-      <c r="N15" s="61">
+      <c r="O15" s="60">
         <f t="shared" si="5"/>
         <v>114480.03</v>
       </c>
-      <c r="O15" s="62">
+      <c r="P15" s="61">
         <f t="shared" si="6"/>
         <v>111240.03</v>
       </c>
-      <c r="P15" s="31">
-        <f t="shared" ref="P15:P30" si="7">P14+0.01</f>
+      <c r="Q15" s="31">
+        <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>4</v>
       </c>
@@ -3256,113 +3312,121 @@
         <v>6.6</v>
       </c>
       <c r="F16" s="56">
-        <v>129700.04</v>
+        <v>132000.04</v>
       </c>
       <c r="G16" s="57">
-        <f>154060-G32</f>
-        <v>129700</v>
+        <f>144000.25-G32</f>
+        <v>132000.04999999999</v>
       </c>
       <c r="H16" s="58">
         <f t="shared" si="0"/>
-        <v>3.9999999993597157E-2</v>
+        <v>-9.9999999802093953E-3</v>
       </c>
       <c r="I16" s="58">
         <f t="shared" si="1"/>
-        <v>1.1999999998079146E-3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="59">
         <f>EDESUR!I8</f>
         <v>0</v>
       </c>
-      <c r="K16" s="117">
+      <c r="K16" s="115">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L16" s="117">
+      <c r="L16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M16" s="60">
+      <c r="M16" s="213">
+        <f>Hoja1!O8</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="211">
         <f t="shared" si="4"/>
         <v>132000.04</v>
       </c>
-      <c r="N16" s="61">
+      <c r="O16" s="60">
         <f t="shared" si="5"/>
         <v>139920.04</v>
       </c>
-      <c r="O16" s="62">
+      <c r="P16" s="61">
         <f t="shared" si="6"/>
         <v>135960.04</v>
       </c>
-      <c r="P16" s="31">
+      <c r="Q16" s="31">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="177">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="165">
         <v>5</v>
       </c>
-      <c r="B17" s="177" t="s">
+      <c r="B17" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="177" t="s">
+      <c r="C17" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="177" t="s">
+      <c r="D17" s="165" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="178">
+      <c r="E17" s="166">
         <v>6.6</v>
       </c>
-      <c r="F17" s="179">
+      <c r="F17" s="167">
         <v>132000.04999999999</v>
       </c>
-      <c r="G17" s="179">
+      <c r="G17" s="167">
         <f t="shared" ref="G17:G21" si="8">F17</f>
         <v>132000.04999999999</v>
       </c>
-      <c r="H17" s="180">
+      <c r="H17" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="180">
+      <c r="I17" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="181">
+      <c r="J17" s="169">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="K17" s="182">
+      <c r="K17" s="170">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L17" s="182">
+      <c r="L17" s="170">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="183">
+      <c r="M17" s="214">
+        <f>Hoja1!O9</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="212">
         <f t="shared" si="4"/>
         <v>132000.04999999999</v>
       </c>
-      <c r="N17" s="184">
+      <c r="O17" s="171">
         <f t="shared" si="5"/>
         <v>139920.04999999999</v>
       </c>
-      <c r="O17" s="185">
+      <c r="P17" s="172">
         <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
-      <c r="P17" s="31">
+      <c r="Q17" s="31">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="Q17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>6</v>
       </c>
@@ -3397,152 +3461,161 @@
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="K18" s="117">
+      <c r="K18" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L18" s="117">
+      <c r="L18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="60">
+      <c r="M18" s="213">
+        <f>Hoja1!O10</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="211">
         <f t="shared" si="4"/>
         <v>108000.06</v>
       </c>
-      <c r="N18" s="61">
+      <c r="O18" s="60">
         <f t="shared" si="5"/>
         <v>114480.06</v>
       </c>
-      <c r="O18" s="62">
+      <c r="P18" s="61">
         <f t="shared" si="6"/>
         <v>111240.06</v>
       </c>
-      <c r="P18" s="31">
+      <c r="Q18" s="31">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="151">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="202">
         <v>7</v>
       </c>
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="151" t="s">
+      <c r="C19" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="202" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="153">
+      <c r="E19" s="204">
         <v>5.4</v>
       </c>
-      <c r="F19" s="154">
+      <c r="F19" s="57">
         <v>108000.07</v>
       </c>
-      <c r="G19" s="154">
-        <f t="shared" si="8"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="205">
+        <f t="shared" si="0"/>
         <v>108000.07</v>
       </c>
-      <c r="H19" s="155">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="155">
+      <c r="I19" s="205">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="156">
+        <v>3240.0021000000002</v>
+      </c>
+      <c r="J19" s="206">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="K19" s="157">
+      <c r="K19" s="207">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L19" s="157">
+      <c r="L19" s="207">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="158">
+      <c r="M19" s="213">
+        <f>Hoja1!O7</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="211">
         <f t="shared" si="4"/>
-        <v>108000.07</v>
-      </c>
-      <c r="N19" s="159">
+        <v>219240.07</v>
+      </c>
+      <c r="O19" s="208">
         <f t="shared" si="5"/>
-        <v>114480.07</v>
-      </c>
-      <c r="O19" s="160">
+        <v>232394.07</v>
+      </c>
+      <c r="P19" s="209">
         <f t="shared" si="6"/>
-        <v>111240.07</v>
-      </c>
-      <c r="P19" s="31">
+        <v>225817.07</v>
+      </c>
+      <c r="Q19" s="31">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="151">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="202">
         <v>8</v>
       </c>
-      <c r="B20" s="151" t="s">
+      <c r="B20" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="151" t="s">
+      <c r="C20" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="152" t="s">
+      <c r="D20" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="153">
+      <c r="E20" s="204">
         <v>6.6</v>
       </c>
-      <c r="F20" s="154">
-        <v>132000.07999999999</v>
-      </c>
-      <c r="G20" s="154">
-        <f t="shared" si="8"/>
-        <v>132000.07999999999</v>
-      </c>
-      <c r="H20" s="155">
+      <c r="F20" s="57">
+        <v>135960.07999999999</v>
+      </c>
+      <c r="G20" s="57">
+        <f>F20</f>
+        <v>135960.07999999999</v>
+      </c>
+      <c r="H20" s="205">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="155">
+      <c r="I20" s="205">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="156">
+      <c r="J20" s="206">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="K20" s="157">
+      <c r="K20" s="207">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L20" s="157">
+      <c r="L20" s="207">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="158">
+      <c r="M20" s="213">
+        <f>Hoja1!O12</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="211">
         <f t="shared" si="4"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="N20" s="159">
+      <c r="O20" s="208">
         <f t="shared" si="5"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="O20" s="160">
+      <c r="P20" s="209">
         <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
-      <c r="P20" s="31">
+      <c r="Q20" s="31">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>9</v>
       </c>
@@ -3577,32 +3650,36 @@
         <f>EDESUR!I13</f>
         <v>0</v>
       </c>
-      <c r="K21" s="117">
+      <c r="K21" s="115">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L21" s="117">
+      <c r="L21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="60">
+      <c r="M21" s="213">
+        <f>Hoja1!O13</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="211">
         <f t="shared" si="4"/>
         <v>132000.09</v>
       </c>
-      <c r="N21" s="61">
+      <c r="O21" s="60">
         <f t="shared" si="5"/>
         <v>139920.09</v>
       </c>
-      <c r="O21" s="62">
+      <c r="P21" s="61">
         <f t="shared" si="6"/>
         <v>135960.09</v>
       </c>
-      <c r="P21" s="31">
+      <c r="Q21" s="31">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>10</v>
       </c>
@@ -3619,11 +3696,11 @@
         <v>5.4</v>
       </c>
       <c r="F22" s="56">
-        <v>68000.100000000006</v>
+        <v>108000.1</v>
       </c>
       <c r="G22" s="57">
         <f>F22</f>
-        <v>68000.100000000006</v>
+        <v>108000.1</v>
       </c>
       <c r="H22" s="58">
         <f t="shared" si="0"/>
@@ -3637,32 +3714,36 @@
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="K22" s="117">
+      <c r="K22" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L22" s="117">
+      <c r="L22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="60">
+      <c r="M22" s="213">
+        <f>Hoja1!O14</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="211">
         <f t="shared" si="4"/>
         <v>108000.1</v>
       </c>
-      <c r="N22" s="61">
+      <c r="O22" s="60">
         <f t="shared" si="5"/>
         <v>114480.1</v>
       </c>
-      <c r="O22" s="62">
+      <c r="P22" s="61">
         <f t="shared" si="6"/>
         <v>111240.1</v>
       </c>
-      <c r="P22" s="31">
+      <c r="Q22" s="31">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>11</v>
       </c>
@@ -3680,12 +3761,12 @@
         <v>108000.11</v>
       </c>
       <c r="G23" s="57">
-        <f>114000.11-G34</f>
-        <v>108000.11</v>
+        <f>114033-G34</f>
+        <v>108032.78</v>
       </c>
       <c r="H23" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-32.669999999998254</v>
       </c>
       <c r="I23" s="58">
         <f t="shared" si="1"/>
@@ -3695,35 +3776,39 @@
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="K23" s="117">
+      <c r="K23" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L23" s="117">
+      <c r="L23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23" s="60">
+      <c r="M23" s="213">
+        <f>Hoja1!O11</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="211">
         <f t="shared" si="4"/>
-        <v>108000.11</v>
-      </c>
-      <c r="N23" s="61">
+        <v>107967.11</v>
+      </c>
+      <c r="O23" s="60">
         <f t="shared" si="5"/>
-        <v>114480.11</v>
-      </c>
-      <c r="O23" s="62">
+        <v>114445.11</v>
+      </c>
+      <c r="P23" s="61">
         <f t="shared" si="6"/>
-        <v>111240.11</v>
-      </c>
-      <c r="P23" s="31">
+        <v>111206.11</v>
+      </c>
+      <c r="Q23" s="31">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>12</v>
       </c>
@@ -3758,32 +3843,36 @@
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="K24" s="117">
+      <c r="K24" s="115">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L24" s="117">
+      <c r="L24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M24" s="60">
+      <c r="M24" s="213">
+        <f>Hoja1!O16</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="211">
         <f t="shared" si="4"/>
         <v>132000.12</v>
       </c>
-      <c r="N24" s="61">
+      <c r="O24" s="60">
         <f t="shared" si="5"/>
         <v>139920.12</v>
       </c>
-      <c r="O24" s="62">
+      <c r="P24" s="61">
         <f t="shared" si="6"/>
         <v>135960.12</v>
       </c>
-      <c r="P24" s="31">
+      <c r="Q24" s="31">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>13</v>
       </c>
@@ -3800,14 +3889,14 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="56">
-        <v>128040.13</v>
+        <v>128159.13</v>
       </c>
       <c r="G25" s="57">
-        <v>131881.13</v>
+        <v>132004.13</v>
       </c>
       <c r="H25" s="58">
         <f t="shared" si="0"/>
-        <v>-3841</v>
+        <v>-3845</v>
       </c>
       <c r="I25" s="58">
         <f t="shared" si="1"/>
@@ -3817,32 +3906,36 @@
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="K25" s="117">
+      <c r="K25" s="115">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L25" s="117">
+      <c r="L25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25" s="60">
+      <c r="M25" s="213">
+        <f>Hoja1!O17</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="211">
         <f t="shared" si="4"/>
-        <v>128159.13</v>
-      </c>
-      <c r="N25" s="61">
+        <v>128155.13</v>
+      </c>
+      <c r="O25" s="60">
         <f t="shared" si="5"/>
-        <v>135849.13</v>
-      </c>
-      <c r="O25" s="62">
+        <v>135844.13</v>
+      </c>
+      <c r="P25" s="61">
         <f t="shared" si="6"/>
-        <v>132004.13</v>
-      </c>
-      <c r="P25" s="31">
+        <v>132000.13</v>
+      </c>
+      <c r="Q25" s="31">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="46">
         <v>14</v>
       </c>
@@ -3857,15 +3950,15 @@
         <v>5.4</v>
       </c>
       <c r="F26" s="56">
-        <v>108000.14</v>
+        <v>83116.14</v>
       </c>
       <c r="G26" s="57">
-        <f>F26+RESUMEN!D41</f>
-        <v>132884.35</v>
+        <f>F26</f>
+        <v>83116.14</v>
       </c>
       <c r="H26" s="58">
         <f t="shared" si="0"/>
-        <v>-24884.210000000006</v>
+        <v>0</v>
       </c>
       <c r="I26" s="58">
         <f t="shared" si="1"/>
@@ -3875,32 +3968,36 @@
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="K26" s="117">
+      <c r="K26" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L26" s="117">
+      <c r="L26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="60">
+      <c r="M26" s="213">
+        <f>Hoja1!O18</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="211">
         <f t="shared" si="4"/>
-        <v>83116.14</v>
-      </c>
-      <c r="N26" s="61">
+        <v>108000.14</v>
+      </c>
+      <c r="O26" s="60">
         <f t="shared" si="5"/>
-        <v>88103.14</v>
-      </c>
-      <c r="O26" s="62">
+        <v>114480.14</v>
+      </c>
+      <c r="P26" s="61">
         <f t="shared" si="6"/>
-        <v>85609.14</v>
-      </c>
-      <c r="P26" s="31">
+        <v>111240.14</v>
+      </c>
+      <c r="Q26" s="31">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46">
         <v>15</v>
       </c>
@@ -3933,32 +4030,36 @@
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="K27" s="117">
+      <c r="K27" s="115">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L27" s="117">
+      <c r="L27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="60">
+      <c r="M27" s="213">
+        <f>Hoja1!O15</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="211">
         <f t="shared" si="4"/>
         <v>108000.15</v>
       </c>
-      <c r="N27" s="61">
+      <c r="O27" s="60">
         <f t="shared" si="5"/>
         <v>114480.15</v>
       </c>
-      <c r="O27" s="62">
+      <c r="P27" s="61">
         <f t="shared" si="6"/>
         <v>111240.15</v>
       </c>
-      <c r="P27" s="31">
+      <c r="Q27" s="31">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>16</v>
       </c>
@@ -3993,32 +4094,36 @@
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K28" s="117">
+      <c r="K28" s="115">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="L28" s="117">
+      <c r="L28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M28" s="60">
+      <c r="M28" s="213">
+        <f>Hoja1!O22</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="211">
         <f t="shared" si="4"/>
         <v>14000.16</v>
       </c>
-      <c r="N28" s="61">
+      <c r="O28" s="60">
         <f t="shared" si="5"/>
         <v>14840.16</v>
       </c>
-      <c r="O28" s="62">
+      <c r="P28" s="61">
         <f t="shared" si="6"/>
         <v>14420.16</v>
       </c>
-      <c r="P28" s="31">
+      <c r="Q28" s="31">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>17</v>
       </c>
@@ -4036,7 +4141,7 @@
         <v>12000.17</v>
       </c>
       <c r="G29" s="57">
-        <f t="shared" ref="G29:G31" si="9">F29</f>
+        <f t="shared" ref="G29" si="9">F29</f>
         <v>12000.17</v>
       </c>
       <c r="H29" s="58">
@@ -4051,32 +4156,36 @@
         <f>EDESUR!I21</f>
         <v>0</v>
       </c>
-      <c r="K29" s="117">
+      <c r="K29" s="115">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L29" s="117">
+      <c r="L29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M29" s="60">
+      <c r="M29" s="213">
+        <f>Hoja1!O23</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="211">
         <f t="shared" si="4"/>
         <v>12000.17</v>
       </c>
-      <c r="N29" s="61">
+      <c r="O29" s="60">
         <f t="shared" si="5"/>
         <v>12720.17</v>
       </c>
-      <c r="O29" s="62">
+      <c r="P29" s="61">
         <f t="shared" si="6"/>
         <v>12360.17</v>
       </c>
-      <c r="P29" s="31">
+      <c r="Q29" s="31">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>18</v>
       </c>
@@ -4086,7 +4195,7 @@
       <c r="C30" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="94"/>
+      <c r="D30" s="92"/>
       <c r="E30" s="55">
         <v>0.6</v>
       </c>
@@ -4094,7 +4203,7 @@
         <v>12000.18</v>
       </c>
       <c r="G30" s="57">
-        <f t="shared" si="9"/>
+        <f>F30</f>
         <v>12000.18</v>
       </c>
       <c r="H30" s="58">
@@ -4109,91 +4218,98 @@
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K30" s="117">
+      <c r="K30" s="115">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L30" s="117">
+      <c r="L30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="60">
+      <c r="M30" s="213">
+        <f>Hoja1!O24</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="211">
         <f t="shared" si="4"/>
         <v>12000.18</v>
       </c>
-      <c r="N30" s="61">
+      <c r="O30" s="60">
         <f t="shared" si="5"/>
         <v>12720.18</v>
       </c>
-      <c r="O30" s="62">
+      <c r="P30" s="61">
         <f t="shared" si="6"/>
         <v>12360.18</v>
       </c>
-      <c r="P30" s="31">
+      <c r="Q30" s="31">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="46">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="165">
         <v>19</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="165" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="165" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="55">
+      <c r="D31" s="201"/>
+      <c r="E31" s="166">
         <v>0.6</v>
       </c>
-      <c r="F31" s="56">
+      <c r="F31" s="167">
         <v>12000.19</v>
       </c>
-      <c r="G31" s="57">
-        <f t="shared" si="9"/>
-        <v>12000.19</v>
-      </c>
-      <c r="H31" s="58">
+      <c r="G31" s="167">
+        <v>12360</v>
+      </c>
+      <c r="H31" s="168">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="58">
+        <v>-359.80999999999949</v>
+      </c>
+      <c r="I31" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="59">
+      <c r="J31" s="169">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="K31" s="117">
+      <c r="K31" s="170">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L31" s="117">
+      <c r="L31" s="170">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="60">
+      <c r="M31" s="214">
+        <f>Hoja1!O25</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="212">
         <f t="shared" si="4"/>
-        <v>12000.19</v>
-      </c>
-      <c r="N31" s="61"/>
-      <c r="O31" s="62">
+        <v>11640.19</v>
+      </c>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172">
         <f t="shared" si="6"/>
-        <v>12360.19</v>
-      </c>
-      <c r="P31" s="31">
-        <f>P30+0.01</f>
+        <v>11989.19</v>
+      </c>
+      <c r="Q31" s="31">
+        <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="63">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="62">
         <v>20</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="62" t="s">
         <v>64</v>
       </c>
       <c r="C32" s="46" t="s">
@@ -4205,12 +4321,12 @@
       <c r="E32" s="55">
         <v>0.6</v>
       </c>
-      <c r="F32" s="65">
-        <v>24360</v>
+      <c r="F32" s="64">
+        <v>12000.2</v>
       </c>
       <c r="G32" s="57">
         <f>F32</f>
-        <v>24360</v>
+        <v>12000.2</v>
       </c>
       <c r="H32" s="58">
         <f t="shared" si="0"/>
@@ -4224,33 +4340,37 @@
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="K32" s="117">
+      <c r="K32" s="115">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L32" s="117">
+      <c r="L32" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M32" s="60">
+      <c r="M32" s="213">
+        <f>Hoja1!O26</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="211">
         <f t="shared" si="4"/>
         <v>12000.2</v>
       </c>
-      <c r="N32" s="61"/>
-      <c r="O32" s="62">
+      <c r="O32" s="60"/>
+      <c r="P32" s="61">
         <f t="shared" si="6"/>
         <v>12360.2</v>
       </c>
-      <c r="P32" s="31">
-        <f t="shared" ref="P32:P35" si="10">P31+0.01</f>
+      <c r="Q32" s="31">
+        <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="63">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="62">
         <v>21</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="62" t="s">
         <v>65</v>
       </c>
       <c r="C33" s="48" t="s">
@@ -4262,12 +4382,12 @@
       <c r="E33" s="55">
         <v>0.3</v>
       </c>
-      <c r="F33" s="65">
-        <v>6000</v>
-      </c>
-      <c r="G33" s="194">
+      <c r="F33" s="64">
+        <v>6000.21</v>
+      </c>
+      <c r="G33" s="181">
         <f>F33</f>
-        <v>6000</v>
+        <v>6000.21</v>
       </c>
       <c r="H33" s="58">
         <f t="shared" si="0"/>
@@ -4281,33 +4401,37 @@
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="K33" s="117">
+      <c r="K33" s="115">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L33" s="117">
+      <c r="L33" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M33" s="60">
+      <c r="M33" s="213">
+        <f>Hoja1!O27</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="211">
         <f t="shared" si="4"/>
         <v>6000.21</v>
       </c>
-      <c r="N33" s="61"/>
-      <c r="O33" s="62">
+      <c r="O33" s="60"/>
+      <c r="P33" s="61">
         <f t="shared" si="6"/>
         <v>6180.21</v>
       </c>
-      <c r="P33" s="31">
+      <c r="Q33" s="31">
         <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="64">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="63">
         <v>22</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="63" t="s">
         <v>66</v>
       </c>
       <c r="C34" s="46" t="s">
@@ -4317,12 +4441,12 @@
       <c r="E34" s="55">
         <v>0.3</v>
       </c>
-      <c r="F34" s="65">
-        <v>6000</v>
-      </c>
-      <c r="G34" s="194">
+      <c r="F34" s="64">
+        <v>6000.22</v>
+      </c>
+      <c r="G34" s="181">
         <f>F34</f>
-        <v>6000</v>
+        <v>6000.22</v>
       </c>
       <c r="H34" s="58">
         <f t="shared" si="0"/>
@@ -4336,36 +4460,40 @@
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="K34" s="117">
+      <c r="K34" s="115">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L34" s="117">
+      <c r="L34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M34" s="60">
+      <c r="M34" s="213">
+        <f>Hoja1!O28</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="211">
         <f t="shared" si="4"/>
         <v>6000.22</v>
       </c>
-      <c r="N34" s="61"/>
-      <c r="O34" s="62">
+      <c r="O34" s="60"/>
+      <c r="P34" s="61">
         <f t="shared" si="6"/>
         <v>6180.22</v>
       </c>
-      <c r="P34" s="31">
+      <c r="Q34" s="31">
         <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46">
         <v>23</v>
       </c>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="65" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="47" t="s">
@@ -4374,12 +4502,12 @@
       <c r="E35" s="55">
         <v>0.3</v>
       </c>
-      <c r="F35" s="65">
-        <v>6000</v>
-      </c>
-      <c r="G35" s="194">
+      <c r="F35" s="64">
+        <v>6000.23</v>
+      </c>
+      <c r="G35" s="181">
         <f>F35</f>
-        <v>6000</v>
+        <v>6000.23</v>
       </c>
       <c r="H35" s="58">
         <f t="shared" si="0"/>
@@ -4393,58 +4521,62 @@
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="K35" s="117">
+      <c r="K35" s="115">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L35" s="117">
+      <c r="L35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="60">
+      <c r="M35" s="213">
+        <f>Hoja1!O29</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="211">
         <f t="shared" si="4"/>
         <v>6000.23</v>
       </c>
-      <c r="N35" s="67"/>
-      <c r="O35" s="62">
+      <c r="O35" s="66"/>
+      <c r="P35" s="61">
         <f t="shared" si="6"/>
         <v>6180.23</v>
       </c>
-      <c r="P35" s="31">
+      <c r="Q35" s="31">
         <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="68"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="129">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="67"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="127">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="F36" s="40">
         <f>SUM(F13:F35)</f>
-        <v>1958183.9000000001</v>
+        <v>1975237.76</v>
       </c>
       <c r="G36" s="44">
         <f>SUM(G13:G35)</f>
-        <v>1986908.7200000002</v>
+        <v>1869474.7999999996</v>
       </c>
       <c r="H36" s="44">
         <f>SUM(H13:H35)</f>
-        <v>-28724.820000000007</v>
+        <v>105762.96000000004</v>
       </c>
       <c r="I36" s="44">
-        <f t="shared" ref="I36:N36" si="11">SUM(I13:I35)</f>
-        <v>1.1699999999982537E-2</v>
+        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
+        <v>3300.0135000000005</v>
       </c>
       <c r="J36" s="44">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K36" s="97">
+      <c r="K36" s="95">
         <f t="shared" si="11"/>
         <v>2000000</v>
       </c>
@@ -4452,125 +4584,133 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="M36" s="70">
-        <f>SUM(M13:M35)</f>
-        <v>1971277.76</v>
-      </c>
-      <c r="N36" s="70">
+      <c r="M36" s="210"/>
+      <c r="N36" s="69">
+        <f>SUM(N13:N35)</f>
+        <v>2118170.7600000002</v>
+      </c>
+      <c r="O36" s="69">
         <f t="shared" si="11"/>
-        <v>2045033.7100000002</v>
-      </c>
-      <c r="O36" s="70">
-        <f>SUM(O13:O35)</f>
-        <v>2030415.76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2201120.7100000009</v>
+      </c>
+      <c r="P36" s="69">
+        <f>SUM(P13:P35)</f>
+        <v>2181715.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="204" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="224" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="204"/>
-      <c r="E39" s="204"/>
-      <c r="F39" s="204"/>
-      <c r="G39" s="204"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="204"/>
-      <c r="J39" s="204"/>
-      <c r="K39" s="204"/>
-      <c r="L39" s="204"/>
-      <c r="M39" s="204"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="204"/>
-      <c r="D40" s="204"/>
-      <c r="E40" s="204"/>
-      <c r="F40" s="204"/>
-      <c r="G40" s="204"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="204"/>
-      <c r="J40" s="204"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="204"/>
-      <c r="M40" s="204"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="204"/>
-      <c r="D41" s="204"/>
-      <c r="E41" s="204"/>
-      <c r="F41" s="204"/>
-      <c r="G41" s="204"/>
-      <c r="H41" s="204"/>
-      <c r="I41" s="204"/>
-      <c r="J41" s="204"/>
-      <c r="K41" s="204"/>
-      <c r="L41" s="204"/>
-      <c r="M41" s="204"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="204"/>
-      <c r="D42" s="204"/>
-      <c r="E42" s="204"/>
-      <c r="F42" s="204"/>
-      <c r="G42" s="204"/>
-      <c r="H42" s="204"/>
-      <c r="I42" s="204"/>
-      <c r="J42" s="204"/>
-      <c r="K42" s="204"/>
-      <c r="L42" s="204"/>
-      <c r="M42" s="204"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="204"/>
-      <c r="D43" s="204"/>
-      <c r="E43" s="204"/>
-      <c r="F43" s="204"/>
-      <c r="G43" s="204"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="204"/>
-      <c r="J43" s="204"/>
-      <c r="K43" s="204"/>
-      <c r="L43" s="204"/>
-      <c r="M43" s="204"/>
-    </row>
-    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="204"/>
-      <c r="D44" s="204"/>
-      <c r="E44" s="204"/>
-      <c r="F44" s="204"/>
-      <c r="G44" s="204"/>
-      <c r="H44" s="204"/>
-      <c r="I44" s="204"/>
-      <c r="J44" s="204"/>
-      <c r="K44" s="204"/>
-      <c r="L44" s="204"/>
-      <c r="M44" s="204"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="224"/>
+      <c r="F39" s="224"/>
+      <c r="G39" s="224"/>
+      <c r="H39" s="224"/>
+      <c r="I39" s="224"/>
+      <c r="J39" s="224"/>
+      <c r="K39" s="224"/>
+      <c r="L39" s="224"/>
+      <c r="M39" s="224"/>
+      <c r="N39" s="224"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="224"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="224"/>
+      <c r="F40" s="224"/>
+      <c r="G40" s="224"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="224"/>
+      <c r="J40" s="224"/>
+      <c r="K40" s="224"/>
+      <c r="L40" s="224"/>
+      <c r="M40" s="224"/>
+      <c r="N40" s="224"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="224"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="224"/>
+      <c r="F41" s="224"/>
+      <c r="G41" s="224"/>
+      <c r="H41" s="224"/>
+      <c r="I41" s="224"/>
+      <c r="J41" s="224"/>
+      <c r="K41" s="224"/>
+      <c r="L41" s="224"/>
+      <c r="M41" s="224"/>
+      <c r="N41" s="224"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="224"/>
+      <c r="K42" s="224"/>
+      <c r="L42" s="224"/>
+      <c r="M42" s="224"/>
+      <c r="N42" s="224"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="224"/>
+      <c r="J43" s="224"/>
+      <c r="K43" s="224"/>
+      <c r="L43" s="224"/>
+      <c r="M43" s="224"/>
+      <c r="N43" s="224"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="224"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="224"/>
+      <c r="G44" s="224"/>
+      <c r="H44" s="224"/>
+      <c r="I44" s="224"/>
+      <c r="J44" s="224"/>
+      <c r="K44" s="224"/>
+      <c r="L44" s="224"/>
+      <c r="M44" s="224"/>
+      <c r="N44" s="224"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="C39:M44"/>
+  <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O11:O12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A4:O8"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A4:P8"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="A9:P9"/>
+    <mergeCell ref="A10:P10"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4578,598 +4718,1534 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F164D2C4-E422-4A1F-8D41-68B110E9BD73}">
+  <dimension ref="B2:O32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="1.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="142" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="143" customWidth="1"/>
+    <col min="14" max="14" width="2" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="197" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="254" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="255" t="s">
+        <v>132</v>
+      </c>
+      <c r="I2" s="256"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="138" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="183" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="138" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="136" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="136" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="136" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="136" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="184" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="136"/>
+      <c r="M3" s="139"/>
+      <c r="O3" s="138"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="136">
+        <v>1</v>
+      </c>
+      <c r="C4" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="185">
+        <v>132.44000000000014</v>
+      </c>
+      <c r="E4" s="186">
+        <v>0.14153201675643337</v>
+      </c>
+      <c r="F4" s="187">
+        <v>27650.646458296778</v>
+      </c>
+      <c r="H4" s="188">
+        <v>0.12</v>
+      </c>
+      <c r="I4" s="189">
+        <v>5091.8611170500353</v>
+      </c>
+      <c r="K4" s="140">
+        <f>I4+F4</f>
+        <v>32742.507575346812</v>
+      </c>
+      <c r="M4" s="190">
+        <f>K4</f>
+        <v>32742.507575346812</v>
+      </c>
+      <c r="O4" s="140">
+        <f>K4-M4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="136">
+        <v>1</v>
+      </c>
+      <c r="C5" s="136" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="191">
+        <v>107.16000000000004</v>
+      </c>
+      <c r="E5" s="186">
+        <v>0.11451654270325724</v>
+      </c>
+      <c r="F5" s="187">
+        <v>22372.721794556637</v>
+      </c>
+      <c r="H5" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I5" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K5" s="140">
+        <f t="shared" ref="K5:K18" si="0">I5+F5</f>
+        <v>25173.245408934155</v>
+      </c>
+      <c r="M5" s="190">
+        <v>16067.263110135304</v>
+      </c>
+      <c r="O5" s="140">
+        <f t="shared" ref="O5:O18" si="1">K5-M5</f>
+        <v>9105.9822987988518</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="136">
+        <v>1</v>
+      </c>
+      <c r="C6" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="191">
+        <v>102.28000000000002</v>
+      </c>
+      <c r="E6" s="186">
+        <v>0.10930153030691628</v>
+      </c>
+      <c r="F6" s="187">
+        <v>21353.881906935912</v>
+      </c>
+      <c r="H6" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I6" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K6" s="140">
+        <f t="shared" si="0"/>
+        <v>23645.219409608428</v>
+      </c>
+      <c r="M6" s="190">
+        <f t="shared" ref="M6:M18" si="2">K6</f>
+        <v>23645.219409608428</v>
+      </c>
+      <c r="O6" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="137">
+        <v>2</v>
+      </c>
+      <c r="C7" s="137" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="185">
+        <v>20.160000000000036</v>
+      </c>
+      <c r="E7" s="186">
+        <v>2.154398563734294E-2</v>
+      </c>
+      <c r="F7" s="187">
+        <v>4208.977896400359</v>
+      </c>
+      <c r="H7" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I7" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K7" s="140">
+        <f t="shared" si="0"/>
+        <v>6500.3153990728752</v>
+      </c>
+      <c r="M7" s="190">
+        <f t="shared" si="2"/>
+        <v>6500.3153990728752</v>
+      </c>
+      <c r="O7" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="137">
+        <v>2</v>
+      </c>
+      <c r="C8" s="137" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="185">
+        <v>0</v>
+      </c>
+      <c r="E8" s="186">
+        <v>0</v>
+      </c>
+      <c r="F8" s="187">
+        <v>0</v>
+      </c>
+      <c r="H8" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I8" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K8" s="140">
+        <f t="shared" si="0"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="M8" s="190">
+        <f t="shared" si="2"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="O8" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="137">
+        <v>2</v>
+      </c>
+      <c r="C9" s="137" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="185">
+        <v>0</v>
+      </c>
+      <c r="E9" s="186">
+        <v>0</v>
+      </c>
+      <c r="F9" s="187">
+        <v>0</v>
+      </c>
+      <c r="H9" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I9" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K9" s="140">
+        <f t="shared" si="0"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="M9" s="190">
+        <f t="shared" si="2"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="O9" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="137">
+        <v>2</v>
+      </c>
+      <c r="C10" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="185">
+        <v>0</v>
+      </c>
+      <c r="E10" s="186">
+        <v>0</v>
+      </c>
+      <c r="F10" s="193">
+        <v>0</v>
+      </c>
+      <c r="H10" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I10" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K10" s="140">
+        <f t="shared" si="0"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="M10" s="190">
+        <f t="shared" si="2"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="O10" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="137">
+        <v>3</v>
+      </c>
+      <c r="C11" s="137" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="185">
+        <v>0</v>
+      </c>
+      <c r="E11" s="186">
+        <v>0</v>
+      </c>
+      <c r="F11" s="187">
+        <v>0</v>
+      </c>
+      <c r="H11" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I11" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K11" s="140">
+        <f t="shared" si="0"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="M11" s="190">
+        <f t="shared" si="2"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="O11" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="136">
+        <v>3</v>
+      </c>
+      <c r="C12" s="136" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="191">
+        <v>253.12000000000006</v>
+      </c>
+      <c r="E12" s="186">
+        <v>0.27049670855774982</v>
+      </c>
+      <c r="F12" s="187">
+        <v>52846.055810359976</v>
+      </c>
+      <c r="H12" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I12" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K12" s="140">
+        <f t="shared" si="0"/>
+        <v>55646.579424737494</v>
+      </c>
+      <c r="M12" s="190">
+        <f t="shared" si="2"/>
+        <v>55646.579424737494</v>
+      </c>
+      <c r="O12" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="137">
+        <v>3</v>
+      </c>
+      <c r="C13" s="137" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="185">
+        <v>0</v>
+      </c>
+      <c r="E13" s="186">
+        <v>0</v>
+      </c>
+      <c r="F13" s="187">
+        <v>0</v>
+      </c>
+      <c r="H13" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I13" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K13" s="140">
+        <f t="shared" si="0"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="M13" s="190">
+        <f t="shared" si="2"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="O13" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="137">
+        <v>3</v>
+      </c>
+      <c r="C14" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="185">
+        <v>0</v>
+      </c>
+      <c r="E14" s="186">
+        <v>0</v>
+      </c>
+      <c r="F14" s="187">
+        <v>0</v>
+      </c>
+      <c r="H14" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I14" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K14" s="140">
+        <f t="shared" si="0"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="M14" s="190">
+        <f t="shared" si="2"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="O14" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="136">
+        <v>4</v>
+      </c>
+      <c r="C15" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="191">
+        <v>281.23999999999978</v>
+      </c>
+      <c r="E15" s="186">
+        <v>0.30054714884158296</v>
+      </c>
+      <c r="F15" s="187">
+        <v>58716.91188410882</v>
+      </c>
+      <c r="H15" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I15" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K15" s="140">
+        <f t="shared" si="0"/>
+        <v>61008.249386781339</v>
+      </c>
+      <c r="M15" s="190">
+        <f t="shared" si="2"/>
+        <v>61008.249386781339</v>
+      </c>
+      <c r="O15" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="137">
+        <v>4</v>
+      </c>
+      <c r="C16" s="137" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="185">
+        <v>0</v>
+      </c>
+      <c r="E16" s="186">
+        <v>0</v>
+      </c>
+      <c r="F16" s="187">
+        <v>0</v>
+      </c>
+      <c r="H16" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I16" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K16" s="140">
+        <f t="shared" si="0"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="M16" s="190">
+        <f t="shared" si="2"/>
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="O16" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="137">
+        <v>4</v>
+      </c>
+      <c r="C17" s="137" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="185">
+        <v>39.36000000000022</v>
+      </c>
+      <c r="E17" s="186">
+        <v>4.2062067196717325E-2</v>
+      </c>
+      <c r="F17" s="187">
+        <v>8217.5282739245413</v>
+      </c>
+      <c r="H17" s="192">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I17" s="189">
+        <v>2800.5236143775196</v>
+      </c>
+      <c r="K17" s="140">
+        <f t="shared" si="0"/>
+        <v>11018.051888302061</v>
+      </c>
+      <c r="M17" s="190">
+        <f t="shared" si="2"/>
+        <v>11018.051888302061</v>
+      </c>
+      <c r="O17" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="137">
+        <v>4</v>
+      </c>
+      <c r="C18" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="185">
+        <v>0</v>
+      </c>
+      <c r="E18" s="186">
+        <v>0</v>
+      </c>
+      <c r="F18" s="187">
+        <v>0</v>
+      </c>
+      <c r="H18" s="192">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I18" s="189">
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="K18" s="140">
+        <f t="shared" si="0"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="M18" s="190">
+        <f t="shared" si="2"/>
+        <v>2291.3375026725157</v>
+      </c>
+      <c r="O18" s="140">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="194"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="195"/>
+      <c r="K19" s="136"/>
+      <c r="M19" s="139"/>
+      <c r="O19" s="138"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="136"/>
+      <c r="C20" s="136" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="191">
+        <f>SUM(D4:D19)</f>
+        <v>935.76000000000033</v>
+      </c>
+      <c r="E20" s="138"/>
+      <c r="F20" s="194">
+        <f>SUM(F4:F19)</f>
+        <v>195366.72402458303</v>
+      </c>
+      <c r="H20" s="196"/>
+      <c r="I20" s="195">
+        <f>SUM(I4:I19)</f>
+        <v>40734.888936400283</v>
+      </c>
+      <c r="K20" s="140">
+        <f>SUM(K4:K19)</f>
+        <v>236101.61296098327</v>
+      </c>
+      <c r="M20" s="141">
+        <f>SUM(M4:M19)</f>
+        <v>226995.63066218441</v>
+      </c>
+      <c r="O20" s="140">
+        <f>SUM(O4:O19)</f>
+        <v>9105.9822987988518</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="136"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="136">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="H22" s="192">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I22" s="189">
+        <v>297.02523182791873</v>
+      </c>
+      <c r="K22" s="189">
+        <f>I22</f>
+        <v>297.02523182791873</v>
+      </c>
+      <c r="M22" s="198">
+        <f>K22</f>
+        <v>297.02523182791873</v>
+      </c>
+      <c r="O22" s="140">
+        <f t="shared" ref="O22:O29" si="3">K22-M22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="136">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="192">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I23" s="189">
+        <v>254.59305585250178</v>
+      </c>
+      <c r="K23" s="189">
+        <f t="shared" ref="K23:K29" si="4">I23</f>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="M23" s="198">
+        <f t="shared" ref="M23:M29" si="5">K23</f>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="O23" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="136">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="192">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I24" s="189">
+        <v>254.59305585250178</v>
+      </c>
+      <c r="K24" s="189">
+        <f t="shared" si="4"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="M24" s="198">
+        <f t="shared" si="5"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="O24" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="136">
+        <v>4</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="192">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I25" s="189">
+        <v>254.59305585250178</v>
+      </c>
+      <c r="K25" s="189">
+        <f t="shared" si="4"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="M25" s="198">
+        <f t="shared" si="5"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="O25" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="136">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="H26" s="192">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I26" s="189">
+        <v>254.59305585250178</v>
+      </c>
+      <c r="K26" s="189">
+        <f t="shared" si="4"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="M26" s="198">
+        <f t="shared" si="5"/>
+        <v>254.59305585250178</v>
+      </c>
+      <c r="O26" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="136">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="H27" s="192">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I27" s="189">
+        <v>127.29652792625089</v>
+      </c>
+      <c r="K27" s="189">
+        <f t="shared" si="4"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="M27" s="198">
+        <f t="shared" si="5"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="O27" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="136">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="H28" s="192">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I28" s="189">
+        <v>127.29652792625089</v>
+      </c>
+      <c r="K28" s="189">
+        <f t="shared" si="4"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="M28" s="198">
+        <f t="shared" si="5"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="O28" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="136">
+        <v>8</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="H29" s="192">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I29" s="189">
+        <v>127.29652792625089</v>
+      </c>
+      <c r="K29" s="189">
+        <f t="shared" si="4"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="M29" s="198">
+        <f t="shared" si="5"/>
+        <v>127.29652792625089</v>
+      </c>
+      <c r="O29" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H30" s="138" t="s">
+        <v>139</v>
+      </c>
+      <c r="I30" s="189">
+        <f>SUM(I22:I29)</f>
+        <v>1697.2870390166786</v>
+      </c>
+      <c r="K30" s="144">
+        <f>SUM(K22:K29)</f>
+        <v>1697.2870390166786</v>
+      </c>
+      <c r="M30" s="141">
+        <f>SUM(M22:M29)</f>
+        <v>1697.2870390166786</v>
+      </c>
+      <c r="O30" s="140">
+        <f>SUM(O22:O29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O31" s="140"/>
+    </row>
+    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="257" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="258"/>
+      <c r="F32" s="199">
+        <v>237798.9</v>
+      </c>
+      <c r="I32" s="200">
+        <f>F20+I20+I30</f>
+        <v>237798.89999999997</v>
+      </c>
+      <c r="K32" s="140">
+        <f>K20+K30</f>
+        <v>237798.89999999994</v>
+      </c>
+      <c r="M32" s="141">
+        <f>M20+M30</f>
+        <v>228692.91770120108</v>
+      </c>
+      <c r="O32" s="140">
+        <f>O20+O30</f>
+        <v>9105.9822987988518</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="D32:E32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="138" t="s">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="138" t="s">
+      <c r="C3" s="136" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="140" t="s">
+      <c r="E3" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="193" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" s="236" t="s">
+      <c r="G3" s="180" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="255" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="237"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="G4" s="141"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="237"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="138">
+      <c r="J3" s="256"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="G4" s="139"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="256"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="136">
         <v>1</v>
       </c>
-      <c r="C5" s="138" t="s">
+      <c r="C5" s="136" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="142">
+      <c r="E5" s="140">
         <v>26132.02</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="143">
+      <c r="G5" s="141">
         <f>E5</f>
         <v>26132.02</v>
       </c>
-      <c r="I5" s="234">
+      <c r="I5" s="259">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="235"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="138">
+      <c r="J5" s="260"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="136">
         <v>1</v>
       </c>
-      <c r="C6" s="138" t="s">
+      <c r="C6" s="136" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="142">
+      <c r="E6" s="140">
         <v>12925.66</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="143">
+      <c r="G6" s="141">
         <f t="shared" ref="G6:G19" si="0">E6</f>
         <v>12925.66</v>
       </c>
-      <c r="I6" s="234">
+      <c r="I6" s="259">
         <f t="shared" ref="I6:I21" si="1">E6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="235"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="138">
+      <c r="J6" s="260"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="136">
         <v>1</v>
       </c>
-      <c r="C7" s="138" t="s">
+      <c r="C7" s="136" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="142">
+      <c r="E7" s="140">
         <v>10709.96</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="143">
+      <c r="G7" s="141">
         <f t="shared" si="0"/>
         <v>10709.96</v>
       </c>
-      <c r="I7" s="234">
+      <c r="I7" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="235"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="138">
+      <c r="J7" s="260"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="136">
         <v>2</v>
       </c>
-      <c r="C8" s="138" t="s">
+      <c r="C8" s="136" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="142">
+      <c r="E8" s="140">
         <v>5448.33</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="143">
+      <c r="G8" s="141">
         <f t="shared" si="0"/>
         <v>5448.33</v>
       </c>
-      <c r="I8" s="234">
+      <c r="I8" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="235"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="139">
+      <c r="J8" s="260"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="137">
         <v>2</v>
       </c>
-      <c r="C9" s="139" t="s">
+      <c r="C9" s="137" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="142">
+      <c r="E9" s="140">
         <v>2716.04</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="143">
+      <c r="G9" s="141">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I9" s="234">
+      <c r="I9" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="235"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="139">
+      <c r="J9" s="260"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="137">
         <v>2</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="142">
+      <c r="E10" s="140">
         <v>2716.04</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="143">
+      <c r="G10" s="141">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I10" s="234">
+      <c r="I10" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="235"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="139">
+      <c r="J10" s="260"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="137">
         <v>2</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="C11" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="142">
+      <c r="E11" s="140">
         <v>2222.21</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="143">
+      <c r="G11" s="141">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I11" s="234">
+      <c r="I11" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="235"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="139">
+      <c r="J11" s="260"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="137">
         <v>3</v>
       </c>
-      <c r="C12" s="139" t="s">
+      <c r="C12" s="137" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="142">
+      <c r="E12" s="140">
         <v>2222.21</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="143">
+      <c r="G12" s="141">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I12" s="234">
+      <c r="I12" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="235"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="138">
+      <c r="J12" s="260"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="136">
         <v>3</v>
       </c>
-      <c r="C13" s="138" t="s">
+      <c r="C13" s="136" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="142">
+      <c r="E13" s="140">
         <v>24018.62</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="143">
+      <c r="G13" s="141">
         <f t="shared" si="0"/>
         <v>24018.62</v>
       </c>
-      <c r="I13" s="234">
+      <c r="I13" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="235"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="139">
+      <c r="J13" s="260"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="137">
         <v>3</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="140">
         <v>2716.04</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="143">
+      <c r="G14" s="141">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I14" s="234">
+      <c r="I14" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="235"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="139">
+      <c r="J14" s="260"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="137">
         <v>3</v>
       </c>
-      <c r="C15" s="139" t="s">
+      <c r="C15" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="142">
+      <c r="E15" s="140">
         <v>2222.21</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="143">
+      <c r="G15" s="141">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I15" s="234">
+      <c r="I15" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="235"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="138">
+      <c r="J15" s="260"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="136">
         <v>4</v>
       </c>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="136" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="142">
+      <c r="E16" s="140">
         <v>36166.800000000003</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="143">
+      <c r="G16" s="141">
         <f t="shared" si="0"/>
         <v>36166.800000000003</v>
       </c>
-      <c r="I16" s="234">
+      <c r="I16" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="235"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="139">
+      <c r="J16" s="260"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="137">
         <v>4</v>
       </c>
-      <c r="C17" s="139" t="s">
+      <c r="C17" s="137" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="142">
+      <c r="E17" s="140">
         <v>2716.04</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="143">
+      <c r="G17" s="141">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I17" s="234">
+      <c r="I17" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="235"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="138">
+      <c r="J17" s="260"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="136">
         <v>4</v>
       </c>
-      <c r="C18" s="138" t="s">
+      <c r="C18" s="136" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="142">
+      <c r="E18" s="140">
         <v>9014.634</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="143">
+      <c r="G18" s="141">
         <f t="shared" si="0"/>
         <v>9014.634</v>
       </c>
-      <c r="I18" s="234">
+      <c r="I18" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="235"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="139">
+      <c r="J18" s="260"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="137">
         <v>4</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="142">
+      <c r="E19" s="140">
         <v>2222.21</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="143">
+      <c r="G19" s="141">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="235"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="G20" s="141"/>
-      <c r="I20" s="234"/>
-      <c r="J20" s="235"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="186" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="186"/>
-      <c r="D21" s="187"/>
-      <c r="E21" s="188">
+      <c r="J19" s="260"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="E20" s="136"/>
+      <c r="G20" s="139"/>
+      <c r="I20" s="259"/>
+      <c r="J20" s="260"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="173" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="173"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="175">
         <f>SUM(E5:E20)</f>
         <v>144169.02399999998</v>
       </c>
-      <c r="F21" s="189"/>
-      <c r="G21" s="188">
+      <c r="F21" s="176"/>
+      <c r="G21" s="175">
         <f>SUM(G5:G20)</f>
         <v>144169.02399999998</v>
       </c>
-      <c r="I21" s="234">
+      <c r="I21" s="259">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="235"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="138" t="s">
+      <c r="J21" s="260"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="138">
+      <c r="C22" s="136">
         <v>1</v>
       </c>
-      <c r="E22" s="148">
+      <c r="E22" s="146">
         <v>288.06</v>
       </c>
-      <c r="G22" s="149">
+      <c r="G22" s="147">
         <f>E22</f>
         <v>288.06</v>
       </c>
-      <c r="I22" s="234">
+      <c r="I22" s="259">
         <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="235"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="138" t="s">
+      <c r="J22" s="260"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="138">
+      <c r="C23" s="136">
         <v>2</v>
       </c>
-      <c r="E23" s="148">
+      <c r="E23" s="146">
         <v>246.91</v>
       </c>
-      <c r="G23" s="149">
+      <c r="G23" s="147">
         <f t="shared" ref="G23:G29" si="3">E23</f>
         <v>246.91</v>
       </c>
-      <c r="I23" s="234">
+      <c r="I23" s="259">
         <f t="shared" ref="I23:I31" si="4">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="235"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="138" t="s">
+      <c r="J23" s="260"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="138">
+      <c r="C24" s="136">
         <v>3</v>
       </c>
-      <c r="E24" s="148">
+      <c r="E24" s="146">
         <v>246.91</v>
       </c>
-      <c r="G24" s="149">
+      <c r="G24" s="147">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I24" s="234">
+      <c r="I24" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="235"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="138" t="s">
+      <c r="J24" s="260"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="138">
+      <c r="C25" s="136">
         <v>4</v>
       </c>
-      <c r="E25" s="148">
+      <c r="E25" s="146">
         <v>246.91</v>
       </c>
-      <c r="G25" s="149">
+      <c r="G25" s="147">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I25" s="234">
+      <c r="I25" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="235"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="138" t="s">
+      <c r="J25" s="260"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="138">
+      <c r="C26" s="136">
         <v>5</v>
       </c>
-      <c r="E26" s="148">
+      <c r="E26" s="146">
         <v>246.91</v>
       </c>
-      <c r="G26" s="149">
+      <c r="G26" s="147">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I26" s="234">
+      <c r="I26" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="235"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="138" t="s">
+      <c r="J26" s="260"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="138">
+      <c r="C27" s="136">
         <v>6</v>
       </c>
-      <c r="E27" s="148">
+      <c r="E27" s="146">
         <v>123.46</v>
       </c>
-      <c r="G27" s="149">
+      <c r="G27" s="147">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I27" s="234">
+      <c r="I27" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="235"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="138" t="s">
+      <c r="J27" s="260"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="138">
+      <c r="C28" s="136">
         <v>7</v>
       </c>
-      <c r="E28" s="148">
+      <c r="E28" s="146">
         <v>123.46</v>
       </c>
-      <c r="G28" s="149">
+      <c r="G28" s="147">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I28" s="234">
+      <c r="I28" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="235"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="138" t="s">
+      <c r="J28" s="260"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="138">
+      <c r="C29" s="136">
         <v>8</v>
       </c>
-      <c r="E29" s="148">
+      <c r="E29" s="146">
         <v>123.46</v>
       </c>
-      <c r="G29" s="149">
+      <c r="G29" s="147">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I29" s="234">
+      <c r="I29" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="235"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="191" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" s="192"/>
-      <c r="D30" s="190"/>
-      <c r="E30" s="188">
+      <c r="J29" s="260"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="178" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="179"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="175">
         <f>SUM(E22:E29)</f>
         <v>1646.0800000000002</v>
       </c>
-      <c r="F30" s="190"/>
-      <c r="G30" s="188">
+      <c r="F30" s="177"/>
+      <c r="G30" s="175">
         <f>SUM(G22:G29)</f>
         <v>1646.0800000000002</v>
       </c>
-      <c r="I30" s="234">
+      <c r="I30" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="235"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="146"/>
-      <c r="G31" s="143"/>
-      <c r="I31" s="234">
+      <c r="J30" s="260"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="144"/>
+      <c r="G31" s="141"/>
+      <c r="I31" s="259">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="235"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="144"/>
-      <c r="G32" s="145"/>
-      <c r="I32" s="234"/>
-      <c r="J32" s="235"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="146">
+      <c r="J31" s="260"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="142"/>
+      <c r="G32" s="143"/>
+      <c r="I32" s="259"/>
+      <c r="J32" s="260"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="144">
         <f>E30+E21</f>
         <v>145815.10399999996</v>
       </c>
-      <c r="G33" s="143">
+      <c r="G33" s="141">
         <f>G21+G30</f>
         <v>145815.10399999996</v>
       </c>
-      <c r="I33" s="234">
+      <c r="I33" s="259">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="235"/>
+      <c r="J33" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
+++ b/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\SALTA 1167\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEA045A-A6FC-4553-887B-90047F09610C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109F7098-0678-457B-B445-2750C577F4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -481,7 +481,7 @@
 Muchas gracias por su colaboración.</t>
   </si>
   <si>
-    <t>Transf 29/01</t>
+    <t>A transferir</t>
   </si>
 </sst>
 </file>
@@ -1512,6 +1512,12 @@
     <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1529,12 +1535,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2047,12 +2047,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="218" t="s">
+      <c r="B3" s="220" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="219"/>
+      <c r="C3" s="220"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="221"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -2090,49 +2090,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="221" t="s">
+      <c r="B8" s="223" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="221"/>
+      <c r="C8" s="223"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="221"/>
-      <c r="C9" s="221"/>
+      <c r="B9" s="223"/>
+      <c r="C9" s="223"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="221"/>
-      <c r="C10" s="221"/>
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="220" t="s">
+      <c r="A13" s="222" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="220"/>
-      <c r="C13" s="220"/>
-      <c r="D13" s="220"/>
-      <c r="E13" s="220"/>
+      <c r="B13" s="222"/>
+      <c r="C13" s="222"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="220"/>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="220"/>
+      <c r="A14" s="222"/>
+      <c r="B14" s="222"/>
+      <c r="C14" s="222"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="220"/>
-      <c r="B15" s="220"/>
-      <c r="C15" s="220"/>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
+      <c r="A15" s="222"/>
+      <c r="B15" s="222"/>
+      <c r="C15" s="222"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="222"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="220"/>
-      <c r="B16" s="220"/>
-      <c r="C16" s="220"/>
-      <c r="D16" s="220"/>
-      <c r="E16" s="220"/>
+      <c r="A16" s="222"/>
+      <c r="B16" s="222"/>
+      <c r="C16" s="222"/>
+      <c r="D16" s="222"/>
+      <c r="E16" s="222"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2158,10 +2158,10 @@
       <c r="E21" s="102"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="216" t="s">
+      <c r="A22" s="218" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="217"/>
+      <c r="B22" s="219"/>
       <c r="C22" s="39"/>
       <c r="D22" s="118">
         <v>465000.72</v>
@@ -2172,8 +2172,8 @@
       <c r="H22" s="91"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="216"/>
-      <c r="B23" s="217"/>
+      <c r="A23" s="218"/>
+      <c r="B23" s="219"/>
       <c r="C23" s="39"/>
       <c r="D23" s="118"/>
       <c r="E23" s="111"/>
@@ -2201,10 +2201,10 @@
       <c r="E25" s="131"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="216" t="s">
+      <c r="A26" s="218" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="217"/>
+      <c r="B26" s="219"/>
       <c r="C26" s="41"/>
       <c r="D26" s="182">
         <v>74584</v>
@@ -2272,13 +2272,13 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="222" t="s">
+      <c r="A32" s="216" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="223"/>
+      <c r="B32" s="217"/>
       <c r="C32" s="5"/>
       <c r="D32" s="112">
-        <v>388176.46</v>
+        <v>358176.46</v>
       </c>
       <c r="E32" s="111" t="s">
         <v>143</v>
@@ -2306,7 +2306,7 @@
       <c r="D34" s="122"/>
       <c r="E34" s="105">
         <f>SUM(D29:D33)</f>
-        <v>691298.65</v>
+        <v>661298.65</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2317,10 +2317,10 @@
       <c r="E35" s="108"/>
     </row>
     <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="218" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="217"/>
+      <c r="B36" s="219"/>
       <c r="C36" s="5"/>
       <c r="D36" s="112">
         <v>75000</v>
@@ -2364,13 +2364,13 @@
       <c r="E39" s="102"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="216" t="s">
+      <c r="A40" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="217"/>
+      <c r="B40" s="219"/>
       <c r="C40" s="39"/>
       <c r="D40" s="118">
-        <v>149700</v>
+        <v>150000</v>
       </c>
       <c r="E40" s="135" t="s">
         <v>149</v>
@@ -2395,7 +2395,7 @@
       <c r="D42" s="119"/>
       <c r="E42" s="132">
         <f>SUM(D40:D41)</f>
-        <v>149700</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2423,7 +2423,7 @@
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="112">
-        <v>20348</v>
+        <v>21725.200000000001</v>
       </c>
       <c r="E45" s="29"/>
     </row>
@@ -2436,7 +2436,7 @@
       <c r="D46" s="78"/>
       <c r="E46" s="133">
         <f>SUM(D44:D45)</f>
-        <v>20348</v>
+        <v>21725.200000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2453,7 +2453,10 @@
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
       <c r="D48" s="80"/>
-      <c r="E48" s="134"/>
+      <c r="E48" s="134">
+        <f>2000000-1550508.57-300</f>
+        <v>449191.42999999993</v>
+      </c>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -2470,7 +2473,7 @@
       <c r="D50" s="83"/>
       <c r="E50" s="84">
         <f>(SUM(E21:E48))</f>
-        <v>1579131.37</v>
+        <v>2000000</v>
       </c>
       <c r="F50" s="101"/>
       <c r="G50" s="31"/>
@@ -2562,7 +2565,7 @@
       </c>
       <c r="B65" s="72">
         <f>E50</f>
-        <v>1579131.37</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2571,7 +2574,7 @@
       </c>
       <c r="B66" s="72">
         <f>E50-E48</f>
-        <v>1579131.37</v>
+        <v>1550808.57</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2613,7 +2616,7 @@
       </c>
       <c r="B72" s="98">
         <f>-B66</f>
-        <v>-1579131.37</v>
+        <v>-1550808.57</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2652,7 +2655,7 @@
       </c>
       <c r="B77" s="97">
         <f>SUM(B71:C76)</f>
-        <v>-700848.90000000014</v>
+        <v>-672526.10000000033</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2689,10 +2692,7 @@
         <f>B100</f>
         <v>0</v>
       </c>
-      <c r="D81" s="31">
-        <f>B84+B77</f>
-        <v>1299151.0999999999</v>
-      </c>
+      <c r="D81" s="31"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
@@ -2800,13 +2800,13 @@
     <mergeCell ref="A88:C89"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
+++ b/2026/SALTA 1167/ENERO/SALTA1167-Enero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\SALTA 1167\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\SALTA 1167\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109F7098-0678-457B-B445-2750C577F4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF5FEDC-D330-49CD-AAF7-EDFA8BBC496F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,20 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$93</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -489,15 +502,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -1135,8 +1148,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="261">
@@ -1160,25 +1173,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1186,15 +1199,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1208,7 +1221,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1216,25 +1229,25 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1242,25 +1255,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1269,56 +1282,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1327,7 +1340,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1337,11 +1350,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1356,10 +1369,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1368,19 +1381,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1395,41 +1408,41 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1439,8 +1452,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1453,16 +1466,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1471,24 +1484,24 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1499,18 +1512,33 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1518,12 +1546,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1536,14 +1558,14 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1560,12 +1582,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1623,9 +1639,6 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1641,18 +1654,18 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2013,21 +2026,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
         <v>78</v>
@@ -2036,7 +2049,7 @@
       <c r="D1" s="51"/>
       <c r="E1" s="52"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
       <c r="B2" s="53" t="s">
         <v>14</v>
@@ -2045,16 +2058,16 @@
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14"/>
-      <c r="B3" s="220" t="s">
+      <c r="B3" s="223" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="221"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2065,7 +2078,7 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>79</v>
       </c>
@@ -2078,7 +2091,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
@@ -2089,57 +2102,57 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="223" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B8" s="226" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="223"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="223"/>
-      <c r="C9" s="223"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="222" t="s">
+      <c r="C8" s="226"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="226"/>
+      <c r="C9" s="226"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B10" s="226"/>
+      <c r="C10" s="226"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="225" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="222"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="222"/>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="222"/>
-      <c r="B15" s="222"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="222"/>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="225"/>
+      <c r="C13" s="225"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="225"/>
+      <c r="B14" s="225"/>
+      <c r="C14" s="225"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="225"/>
+      <c r="B15" s="225"/>
+      <c r="C15" s="225"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="225"/>
+      <c r="B16" s="225"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>108</v>
       </c>
@@ -2148,7 +2161,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>81</v>
       </c>
@@ -2157,11 +2170,11 @@
       <c r="D21" s="117"/>
       <c r="E21" s="102"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="218" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="216" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="219"/>
+      <c r="B22" s="217"/>
       <c r="C22" s="39"/>
       <c r="D22" s="118">
         <v>465000.72</v>
@@ -2171,15 +2184,15 @@
       </c>
       <c r="H22" s="91"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="218"/>
-      <c r="B23" s="219"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="216"/>
+      <c r="B23" s="217"/>
       <c r="C23" s="39"/>
       <c r="D23" s="118"/>
       <c r="E23" s="111"/>
       <c r="H23" s="91"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
@@ -2191,7 +2204,7 @@
         <v>465000.72</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="25" t="s">
         <v>18</v>
       </c>
@@ -2200,11 +2213,11 @@
       <c r="D25" s="120"/>
       <c r="E25" s="131"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="218" t="s">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="219"/>
+      <c r="B26" s="217"/>
       <c r="C26" s="41"/>
       <c r="D26" s="182">
         <v>74584</v>
@@ -2213,7 +2226,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
@@ -2225,7 +2238,7 @@
         <v>74584</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
@@ -2234,7 +2247,7 @@
       <c r="D28" s="121"/>
       <c r="E28" s="107"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>70</v>
       </c>
@@ -2245,7 +2258,7 @@
       </c>
       <c r="E29" s="111"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>69</v>
       </c>
@@ -2258,7 +2271,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
@@ -2271,11 +2284,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="216" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="221" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="217"/>
+      <c r="B32" s="222"/>
       <c r="C32" s="5"/>
       <c r="D32" s="112">
         <v>358176.46</v>
@@ -2284,7 +2297,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="114" t="s">
         <v>82</v>
       </c>
@@ -2297,7 +2310,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
@@ -2309,18 +2322,18 @@
         <v>661298.65</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="119"/>
       <c r="E35" s="108"/>
     </row>
-    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="218" t="s">
+    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="216" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="219"/>
+      <c r="B36" s="217"/>
       <c r="C36" s="5"/>
       <c r="D36" s="112">
         <v>75000</v>
@@ -2329,7 +2342,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="129" t="s">
         <v>126</v>
       </c>
@@ -2342,7 +2355,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
         <v>6</v>
       </c>
@@ -2354,7 +2367,7 @@
         <v>178200</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="25" t="s">
         <v>11</v>
       </c>
@@ -2363,11 +2376,11 @@
       <c r="D39" s="117"/>
       <c r="E39" s="102"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="218" t="s">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="216" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="219"/>
+      <c r="B40" s="217"/>
       <c r="C40" s="39"/>
       <c r="D40" s="118">
         <v>150000</v>
@@ -2379,14 +2392,14 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="129"/>
       <c r="B41" s="130"/>
       <c r="C41" s="39"/>
       <c r="D41" s="145"/>
       <c r="E41" s="135"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>9</v>
       </c>
@@ -2398,7 +2411,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="25" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2420,7 @@
       <c r="D43" s="116"/>
       <c r="E43" s="103"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>28</v>
       </c>
@@ -2416,7 +2429,7 @@
       <c r="D44" s="112"/>
       <c r="E44" s="109"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>120</v>
       </c>
@@ -2427,7 +2440,7 @@
       </c>
       <c r="E45" s="29"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="38" t="s">
         <v>9</v>
       </c>
@@ -2439,14 +2452,14 @@
         <v>21725.200000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="73"/>
       <c r="E47" s="79"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="22" t="s">
         <v>104</v>
       </c>
@@ -2458,13 +2471,13 @@
         <v>449191.42999999993</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
       <c r="D49" s="81"/>
       <c r="E49" s="82"/>
       <c r="F49" s="31"/>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
         <v>100</v>
       </c>
@@ -2478,16 +2491,16 @@
       <c r="F50" s="101"/>
       <c r="G50" s="31"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D51" s="81"/>
       <c r="E51" s="81"/>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D52" s="81"/>
       <c r="E52" s="81"/>
       <c r="H52" s="123"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>101</v>
       </c>
@@ -2496,35 +2509,35 @@
       <c r="D53" s="85"/>
       <c r="E53" s="86"/>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="75"/>
       <c r="B54" s="110"/>
       <c r="C54" s="5"/>
       <c r="D54" s="76"/>
       <c r="E54" s="74"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="226"/>
-      <c r="B55" s="226"/>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="220"/>
+      <c r="B55" s="220"/>
       <c r="C55" s="5"/>
       <c r="D55" s="112"/>
       <c r="E55" s="74"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="75"/>
       <c r="B57" s="77"/>
       <c r="C57" s="5"/>
       <c r="D57" s="76"/>
       <c r="E57" s="74"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="36"/>
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
@@ -2534,9 +2547,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="22" t="s">
         <v>103</v>
       </c>
@@ -2545,8 +2558,8 @@
       <c r="D61" s="23"/>
       <c r="E61" s="215"/>
     </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
         <v>102</v>
       </c>
@@ -2558,8 +2571,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="71" t="s">
         <v>109</v>
       </c>
@@ -2568,7 +2581,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="71" t="s">
         <v>110</v>
       </c>
@@ -2577,7 +2590,7 @@
         <v>1550808.57</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="71" t="s">
         <v>111</v>
       </c>
@@ -2586,7 +2599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="71" t="s">
         <v>112</v>
       </c>
@@ -2595,12 +2608,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70"/>
       <c r="B70" s="30"/>
       <c r="C70" s="27"/>
     </row>
-    <row r="71" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="93" t="s">
         <v>113</v>
       </c>
@@ -2610,7 +2623,7 @@
       <c r="C71" s="27"/>
       <c r="D71" s="34"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="41" t="s">
         <v>106</v>
       </c>
@@ -2619,7 +2632,7 @@
         <v>-1550808.57</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="41" t="s">
         <v>27</v>
       </c>
@@ -2628,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="41" t="s">
         <v>115</v>
       </c>
@@ -2637,19 +2650,19 @@
         <v>1869474.7999999996</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="41" t="s">
         <v>141</v>
       </c>
       <c r="B75" s="99"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B76" s="124"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="96" t="s">
         <v>117</v>
       </c>
@@ -2658,13 +2671,13 @@
         <v>-672526.10000000033</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="94"/>
       <c r="B78" s="94"/>
       <c r="D78" s="31"/>
       <c r="E78" s="30"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="93" t="s">
         <v>114</v>
       </c>
@@ -2674,7 +2687,7 @@
       <c r="D79" s="30"/>
       <c r="E79" s="31"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="41" t="s">
         <v>107</v>
       </c>
@@ -2684,7 +2697,7 @@
       </c>
       <c r="D80" s="31"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="41" t="s">
         <v>27</v>
       </c>
@@ -2694,7 +2707,7 @@
       </c>
       <c r="D81" s="31"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="41" t="s">
         <v>116</v>
       </c>
@@ -2702,13 +2715,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B83" s="124"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="96" t="s">
         <v>118</v>
       </c>
@@ -2717,28 +2730,28 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="94"/>
       <c r="B85" s="94"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="94"/>
       <c r="B86" s="94"/>
     </row>
-    <row r="87" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="225" t="s">
+    <row r="87" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A88" s="219" t="s">
         <v>19</v>
       </c>
-      <c r="B88" s="225"/>
-      <c r="C88" s="225"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="225"/>
-      <c r="B89" s="225"/>
-      <c r="C89" s="225"/>
-    </row>
-    <row r="90" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="219"/>
+      <c r="C88" s="219"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A89" s="219"/>
+      <c r="B89" s="219"/>
+      <c r="C89" s="219"/>
+    </row>
+    <row r="90" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="88"/>
       <c r="B90" s="26"/>
       <c r="C90" s="26">
@@ -2746,13 +2759,13 @@
       </c>
       <c r="E90" s="101"/>
     </row>
-    <row r="91" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="88"/>
       <c r="B91" s="90"/>
       <c r="C91" s="87"/>
       <c r="D91" s="101"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="32" t="s">
         <v>6</v>
       </c>
@@ -2762,44 +2775,39 @@
       </c>
       <c r="C92" s="33"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M93" s="6"/>
     </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="224"/>
-      <c r="B94" s="224"/>
-      <c r="C94" s="224"/>
-      <c r="D94" s="224"/>
-      <c r="E94" s="224"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="224"/>
-      <c r="B95" s="224"/>
-      <c r="C95" s="224"/>
-      <c r="D95" s="224"/>
-      <c r="E95" s="224"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="224"/>
-      <c r="B96" s="224"/>
-      <c r="C96" s="224"/>
-      <c r="D96" s="224"/>
-      <c r="E96" s="224"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="224"/>
-      <c r="B97" s="224"/>
-      <c r="C97" s="224"/>
-      <c r="D97" s="224"/>
-      <c r="E97" s="224"/>
+    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="218"/>
+      <c r="B94" s="218"/>
+      <c r="C94" s="218"/>
+      <c r="D94" s="218"/>
+      <c r="E94" s="218"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A95" s="218"/>
+      <c r="B95" s="218"/>
+      <c r="C95" s="218"/>
+      <c r="D95" s="218"/>
+      <c r="E95" s="218"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A96" s="218"/>
+      <c r="B96" s="218"/>
+      <c r="C96" s="218"/>
+      <c r="D96" s="218"/>
+      <c r="E96" s="218"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="218"/>
+      <c r="B97" s="218"/>
+      <c r="C97" s="218"/>
+      <c r="D97" s="218"/>
+      <c r="E97" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A94:E97"/>
-    <mergeCell ref="A88:C89"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2807,6 +2815,11 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A94:E97"/>
+    <mergeCell ref="A88:C89"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2817,47 +2830,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.26953125" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" customWidth="1"/>
+    <col min="14" max="14" width="14.7265625" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" customWidth="1"/>
-    <col min="17" max="17" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.26953125" customWidth="1"/>
+    <col min="17" max="17" width="7.26953125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="149"/>
       <c r="B1" s="150"/>
       <c r="C1" s="151"/>
       <c r="D1" s="151"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
+      <c r="E1" s="230"/>
+      <c r="F1" s="230"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
       <c r="O1" s="150"/>
       <c r="P1" s="152"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="153"/>
       <c r="B2" s="154"/>
       <c r="C2" s="155"/>
@@ -2884,7 +2897,7 @@
       <c r="P2" s="162"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="153"/>
       <c r="B3" s="154"/>
       <c r="C3" s="155"/>
@@ -2903,212 +2916,212 @@
       <c r="P3" s="162"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="239" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="240" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="240"/>
-      <c r="C4" s="240"/>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="M4" s="240"/>
-      <c r="N4" s="240"/>
-      <c r="O4" s="240"/>
-      <c r="P4" s="241"/>
+      <c r="B4" s="241"/>
+      <c r="C4" s="241"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="241"/>
+      <c r="N4" s="241"/>
+      <c r="O4" s="241"/>
+      <c r="P4" s="242"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="242"/>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="243"/>
-      <c r="G5" s="243"/>
-      <c r="H5" s="243"/>
-      <c r="I5" s="243"/>
-      <c r="J5" s="243"/>
-      <c r="K5" s="243"/>
-      <c r="L5" s="243"/>
-      <c r="M5" s="243"/>
-      <c r="N5" s="243"/>
-      <c r="O5" s="243"/>
-      <c r="P5" s="244"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="243"/>
+      <c r="B5" s="244"/>
+      <c r="C5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="M5" s="244"/>
+      <c r="N5" s="244"/>
+      <c r="O5" s="244"/>
+      <c r="P5" s="245"/>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="242"/>
-      <c r="B6" s="243"/>
-      <c r="C6" s="243"/>
-      <c r="D6" s="243"/>
-      <c r="E6" s="243"/>
-      <c r="F6" s="243"/>
-      <c r="G6" s="243"/>
-      <c r="H6" s="243"/>
-      <c r="I6" s="243"/>
-      <c r="J6" s="243"/>
-      <c r="K6" s="243"/>
-      <c r="L6" s="243"/>
-      <c r="M6" s="243"/>
-      <c r="N6" s="243"/>
-      <c r="O6" s="243"/>
-      <c r="P6" s="244"/>
+    <row r="6" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="243"/>
+      <c r="B6" s="244"/>
+      <c r="C6" s="244"/>
+      <c r="D6" s="244"/>
+      <c r="E6" s="244"/>
+      <c r="F6" s="244"/>
+      <c r="G6" s="244"/>
+      <c r="H6" s="244"/>
+      <c r="I6" s="244"/>
+      <c r="J6" s="244"/>
+      <c r="K6" s="244"/>
+      <c r="L6" s="244"/>
+      <c r="M6" s="244"/>
+      <c r="N6" s="244"/>
+      <c r="O6" s="244"/>
+      <c r="P6" s="245"/>
       <c r="Q6" s="20"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="242"/>
-      <c r="B7" s="243"/>
-      <c r="C7" s="243"/>
-      <c r="D7" s="243"/>
-      <c r="E7" s="243"/>
-      <c r="F7" s="243"/>
-      <c r="G7" s="243"/>
-      <c r="H7" s="243"/>
-      <c r="I7" s="243"/>
-      <c r="J7" s="243"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="243"/>
-      <c r="M7" s="243"/>
-      <c r="N7" s="243"/>
-      <c r="O7" s="243"/>
-      <c r="P7" s="244"/>
+    <row r="7" spans="1:17" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="244"/>
+      <c r="D7" s="244"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="244"/>
+      <c r="I7" s="244"/>
+      <c r="J7" s="244"/>
+      <c r="K7" s="244"/>
+      <c r="L7" s="244"/>
+      <c r="M7" s="244"/>
+      <c r="N7" s="244"/>
+      <c r="O7" s="244"/>
+      <c r="P7" s="245"/>
       <c r="Q7" s="20"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="245"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="246"/>
-      <c r="D8" s="246"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="246"/>
-      <c r="G8" s="246"/>
-      <c r="H8" s="246"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="246"/>
-      <c r="K8" s="246"/>
-      <c r="L8" s="246"/>
-      <c r="M8" s="246"/>
-      <c r="N8" s="246"/>
-      <c r="O8" s="246"/>
-      <c r="P8" s="247"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="250" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="246"/>
+      <c r="B8" s="247"/>
+      <c r="C8" s="247"/>
+      <c r="D8" s="247"/>
+      <c r="E8" s="247"/>
+      <c r="F8" s="247"/>
+      <c r="G8" s="247"/>
+      <c r="H8" s="247"/>
+      <c r="I8" s="247"/>
+      <c r="J8" s="247"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="247"/>
+      <c r="M8" s="247"/>
+      <c r="N8" s="247"/>
+      <c r="O8" s="247"/>
+      <c r="P8" s="248"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="251" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="251"/>
-      <c r="C9" s="251"/>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
-      <c r="M9" s="251"/>
-      <c r="N9" s="251"/>
-      <c r="O9" s="251"/>
-      <c r="P9" s="251"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="252" t="s">
+      <c r="B9" s="252"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="252"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="252"/>
+      <c r="G9" s="252"/>
+      <c r="H9" s="252"/>
+      <c r="I9" s="252"/>
+      <c r="J9" s="252"/>
+      <c r="K9" s="252"/>
+      <c r="L9" s="252"/>
+      <c r="M9" s="252"/>
+      <c r="N9" s="252"/>
+      <c r="O9" s="252"/>
+      <c r="P9" s="252"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="253" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="252"/>
-      <c r="C10" s="252"/>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
-      <c r="M10" s="252"/>
-      <c r="N10" s="252"/>
-      <c r="O10" s="252"/>
-      <c r="P10" s="252"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="232" t="s">
+      <c r="B10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
+      <c r="M10" s="253"/>
+      <c r="N10" s="253"/>
+      <c r="O10" s="253"/>
+      <c r="P10" s="253"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="227" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="125"/>
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="227" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="232" t="s">
+      <c r="D11" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="232" t="s">
+      <c r="E11" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="228" t="s">
+      <c r="F11" s="231" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="232" t="s">
+      <c r="G11" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="234" t="s">
+      <c r="H11" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="228" t="s">
+      <c r="I11" s="231" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="228" t="s">
+      <c r="J11" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="228" t="s">
+      <c r="K11" s="231" t="s">
         <v>98</v>
       </c>
-      <c r="L11" s="237" t="s">
+      <c r="L11" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="M11" s="228" t="s">
+      <c r="M11" s="231" t="s">
         <v>83</v>
       </c>
       <c r="N11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="230" t="s">
+      <c r="O11" s="233" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="248" t="s">
+      <c r="P11" s="249" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="233"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="229"/>
       <c r="B12" s="126"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="253"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="235"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="229"/>
-      <c r="L12" s="238"/>
-      <c r="M12" s="229"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="228"/>
+      <c r="E12" s="229"/>
+      <c r="F12" s="232"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="237"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="232"/>
       <c r="N12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="O12" s="231"/>
-      <c r="P12" s="249"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="234"/>
+      <c r="P12" s="250"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="46">
         <v>1</v>
       </c>
@@ -3169,7 +3182,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="46">
         <v>2</v>
       </c>
@@ -3215,15 +3228,15 @@
         <v>9105.9822987988518</v>
       </c>
       <c r="N14" s="211">
-        <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
+        <f>ROUND(SUM(H14:M14),0) + Q14</f>
         <v>143166.01999999999</v>
       </c>
       <c r="O14" s="60">
-        <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
+        <f t="shared" ref="O14:O30" si="4">ROUND(N14*6% + N14,0) + Q14</f>
         <v>151756.01999999999</v>
       </c>
       <c r="P14" s="61">
-        <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
+        <f t="shared" ref="P14:P35" si="5">ROUND(N14*3%,0) + N14</f>
         <v>147461.01999999999</v>
       </c>
       <c r="Q14" s="31">
@@ -3231,7 +3244,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="46">
         <v>3</v>
       </c>
@@ -3279,15 +3292,15 @@
         <v>0</v>
       </c>
       <c r="N15" s="211">
+        <f t="shared" ref="N14:N35" si="6">ROUND(SUM(H15:M15),0) + Q15</f>
+        <v>108000.03</v>
+      </c>
+      <c r="O15" s="60">
         <f t="shared" si="4"/>
-        <v>108000.03</v>
-      </c>
-      <c r="O15" s="60">
+        <v>114480.03</v>
+      </c>
+      <c r="P15" s="61">
         <f t="shared" si="5"/>
-        <v>114480.03</v>
-      </c>
-      <c r="P15" s="61">
-        <f t="shared" si="6"/>
         <v>111240.03</v>
       </c>
       <c r="Q15" s="31">
@@ -3295,7 +3308,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
         <v>4</v>
       </c>
@@ -3343,15 +3356,15 @@
         <v>0</v>
       </c>
       <c r="N16" s="211">
+        <f t="shared" si="6"/>
+        <v>132000.04</v>
+      </c>
+      <c r="O16" s="60">
         <f t="shared" si="4"/>
-        <v>132000.04</v>
-      </c>
-      <c r="O16" s="60">
+        <v>139920.04</v>
+      </c>
+      <c r="P16" s="61">
         <f t="shared" si="5"/>
-        <v>139920.04</v>
-      </c>
-      <c r="P16" s="61">
-        <f t="shared" si="6"/>
         <v>135960.04</v>
       </c>
       <c r="Q16" s="31">
@@ -3359,7 +3372,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="165">
         <v>5</v>
       </c>
@@ -3407,15 +3420,15 @@
         <v>0</v>
       </c>
       <c r="N17" s="212">
+        <f t="shared" si="6"/>
+        <v>132000.04999999999</v>
+      </c>
+      <c r="O17" s="171">
         <f t="shared" si="4"/>
-        <v>132000.04999999999</v>
-      </c>
-      <c r="O17" s="171">
+        <v>139920.04999999999</v>
+      </c>
+      <c r="P17" s="172">
         <f t="shared" si="5"/>
-        <v>139920.04999999999</v>
-      </c>
-      <c r="P17" s="172">
-        <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
       <c r="Q17" s="31">
@@ -3426,7 +3439,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
         <v>6</v>
       </c>
@@ -3474,15 +3487,15 @@
         <v>0</v>
       </c>
       <c r="N18" s="211">
+        <f t="shared" si="6"/>
+        <v>108000.06</v>
+      </c>
+      <c r="O18" s="60">
         <f t="shared" si="4"/>
-        <v>108000.06</v>
-      </c>
-      <c r="O18" s="60">
+        <v>114480.06</v>
+      </c>
+      <c r="P18" s="61">
         <f t="shared" si="5"/>
-        <v>114480.06</v>
-      </c>
-      <c r="P18" s="61">
-        <f t="shared" si="6"/>
         <v>111240.06</v>
       </c>
       <c r="Q18" s="31">
@@ -3490,7 +3503,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="202">
         <v>7</v>
       </c>
@@ -3535,15 +3548,15 @@
         <v>0</v>
       </c>
       <c r="N19" s="211">
+        <f t="shared" si="6"/>
+        <v>219240.07</v>
+      </c>
+      <c r="O19" s="208">
         <f t="shared" si="4"/>
-        <v>219240.07</v>
-      </c>
-      <c r="O19" s="208">
+        <v>232394.07</v>
+      </c>
+      <c r="P19" s="209">
         <f t="shared" si="5"/>
-        <v>232394.07</v>
-      </c>
-      <c r="P19" s="209">
-        <f t="shared" si="6"/>
         <v>225817.07</v>
       </c>
       <c r="Q19" s="31">
@@ -3551,7 +3564,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="202">
         <v>8</v>
       </c>
@@ -3599,15 +3612,15 @@
         <v>0</v>
       </c>
       <c r="N20" s="211">
+        <f t="shared" si="6"/>
+        <v>132000.07999999999</v>
+      </c>
+      <c r="O20" s="208">
         <f t="shared" si="4"/>
-        <v>132000.07999999999</v>
-      </c>
-      <c r="O20" s="208">
+        <v>139920.07999999999</v>
+      </c>
+      <c r="P20" s="209">
         <f t="shared" si="5"/>
-        <v>139920.07999999999</v>
-      </c>
-      <c r="P20" s="209">
-        <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
       <c r="Q20" s="31">
@@ -3615,7 +3628,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="46">
         <v>9</v>
       </c>
@@ -3663,15 +3676,15 @@
         <v>0</v>
       </c>
       <c r="N21" s="211">
+        <f t="shared" si="6"/>
+        <v>132000.09</v>
+      </c>
+      <c r="O21" s="60">
         <f t="shared" si="4"/>
-        <v>132000.09</v>
-      </c>
-      <c r="O21" s="60">
+        <v>139920.09</v>
+      </c>
+      <c r="P21" s="61">
         <f t="shared" si="5"/>
-        <v>139920.09</v>
-      </c>
-      <c r="P21" s="61">
-        <f t="shared" si="6"/>
         <v>135960.09</v>
       </c>
       <c r="Q21" s="31">
@@ -3679,7 +3692,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="46">
         <v>10</v>
       </c>
@@ -3727,15 +3740,15 @@
         <v>0</v>
       </c>
       <c r="N22" s="211">
+        <f t="shared" si="6"/>
+        <v>108000.1</v>
+      </c>
+      <c r="O22" s="60">
         <f t="shared" si="4"/>
-        <v>108000.1</v>
-      </c>
-      <c r="O22" s="60">
+        <v>114480.1</v>
+      </c>
+      <c r="P22" s="61">
         <f t="shared" si="5"/>
-        <v>114480.1</v>
-      </c>
-      <c r="P22" s="61">
-        <f t="shared" si="6"/>
         <v>111240.1</v>
       </c>
       <c r="Q22" s="31">
@@ -3743,7 +3756,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="46">
         <v>11</v>
       </c>
@@ -3789,15 +3802,15 @@
         <v>0</v>
       </c>
       <c r="N23" s="211">
+        <f t="shared" si="6"/>
+        <v>107967.11</v>
+      </c>
+      <c r="O23" s="60">
         <f t="shared" si="4"/>
-        <v>107967.11</v>
-      </c>
-      <c r="O23" s="60">
+        <v>114445.11</v>
+      </c>
+      <c r="P23" s="61">
         <f t="shared" si="5"/>
-        <v>114445.11</v>
-      </c>
-      <c r="P23" s="61">
-        <f t="shared" si="6"/>
         <v>111206.11</v>
       </c>
       <c r="Q23" s="31">
@@ -3808,7 +3821,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="46">
         <v>12</v>
       </c>
@@ -3856,15 +3869,15 @@
         <v>0</v>
       </c>
       <c r="N24" s="211">
+        <f t="shared" si="6"/>
+        <v>132000.12</v>
+      </c>
+      <c r="O24" s="60">
         <f t="shared" si="4"/>
-        <v>132000.12</v>
-      </c>
-      <c r="O24" s="60">
+        <v>139920.12</v>
+      </c>
+      <c r="P24" s="61">
         <f t="shared" si="5"/>
-        <v>139920.12</v>
-      </c>
-      <c r="P24" s="61">
-        <f t="shared" si="6"/>
         <v>135960.12</v>
       </c>
       <c r="Q24" s="31">
@@ -3872,7 +3885,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="46">
         <v>13</v>
       </c>
@@ -3919,15 +3932,15 @@
         <v>0</v>
       </c>
       <c r="N25" s="211">
+        <f t="shared" si="6"/>
+        <v>128155.13</v>
+      </c>
+      <c r="O25" s="60">
         <f t="shared" si="4"/>
-        <v>128155.13</v>
-      </c>
-      <c r="O25" s="60">
+        <v>135844.13</v>
+      </c>
+      <c r="P25" s="61">
         <f t="shared" si="5"/>
-        <v>135844.13</v>
-      </c>
-      <c r="P25" s="61">
-        <f t="shared" si="6"/>
         <v>132000.13</v>
       </c>
       <c r="Q25" s="31">
@@ -3935,7 +3948,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="46">
         <v>14</v>
       </c>
@@ -3981,15 +3994,15 @@
         <v>0</v>
       </c>
       <c r="N26" s="211">
+        <f t="shared" si="6"/>
+        <v>108000.14</v>
+      </c>
+      <c r="O26" s="60">
         <f t="shared" si="4"/>
-        <v>108000.14</v>
-      </c>
-      <c r="O26" s="60">
+        <v>114480.14</v>
+      </c>
+      <c r="P26" s="61">
         <f t="shared" si="5"/>
-        <v>114480.14</v>
-      </c>
-      <c r="P26" s="61">
-        <f t="shared" si="6"/>
         <v>111240.14</v>
       </c>
       <c r="Q26" s="31">
@@ -3997,7 +4010,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="46">
         <v>15</v>
       </c>
@@ -4043,15 +4056,15 @@
         <v>0</v>
       </c>
       <c r="N27" s="211">
+        <f t="shared" si="6"/>
+        <v>108000.15</v>
+      </c>
+      <c r="O27" s="60">
         <f t="shared" si="4"/>
-        <v>108000.15</v>
-      </c>
-      <c r="O27" s="60">
+        <v>114480.15</v>
+      </c>
+      <c r="P27" s="61">
         <f t="shared" si="5"/>
-        <v>114480.15</v>
-      </c>
-      <c r="P27" s="61">
-        <f t="shared" si="6"/>
         <v>111240.15</v>
       </c>
       <c r="Q27" s="31">
@@ -4059,7 +4072,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="46">
         <v>16</v>
       </c>
@@ -4107,15 +4120,15 @@
         <v>0</v>
       </c>
       <c r="N28" s="211">
+        <f t="shared" si="6"/>
+        <v>14000.16</v>
+      </c>
+      <c r="O28" s="60">
         <f t="shared" si="4"/>
-        <v>14000.16</v>
-      </c>
-      <c r="O28" s="60">
+        <v>14840.16</v>
+      </c>
+      <c r="P28" s="61">
         <f t="shared" si="5"/>
-        <v>14840.16</v>
-      </c>
-      <c r="P28" s="61">
-        <f t="shared" si="6"/>
         <v>14420.16</v>
       </c>
       <c r="Q28" s="31">
@@ -4123,7 +4136,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="46">
         <v>17</v>
       </c>
@@ -4169,15 +4182,15 @@
         <v>0</v>
       </c>
       <c r="N29" s="211">
+        <f t="shared" si="6"/>
+        <v>12000.17</v>
+      </c>
+      <c r="O29" s="60">
         <f t="shared" si="4"/>
-        <v>12000.17</v>
-      </c>
-      <c r="O29" s="60">
+        <v>12720.17</v>
+      </c>
+      <c r="P29" s="61">
         <f t="shared" si="5"/>
-        <v>12720.17</v>
-      </c>
-      <c r="P29" s="61">
-        <f t="shared" si="6"/>
         <v>12360.17</v>
       </c>
       <c r="Q29" s="31">
@@ -4185,7 +4198,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="46">
         <v>18</v>
       </c>
@@ -4231,15 +4244,15 @@
         <v>0</v>
       </c>
       <c r="N30" s="211">
+        <f t="shared" si="6"/>
+        <v>12000.18</v>
+      </c>
+      <c r="O30" s="60">
         <f t="shared" si="4"/>
-        <v>12000.18</v>
-      </c>
-      <c r="O30" s="60">
+        <v>12720.18</v>
+      </c>
+      <c r="P30" s="61">
         <f t="shared" si="5"/>
-        <v>12720.18</v>
-      </c>
-      <c r="P30" s="61">
-        <f t="shared" si="6"/>
         <v>12360.18</v>
       </c>
       <c r="Q30" s="31">
@@ -4247,7 +4260,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="165">
         <v>19</v>
       </c>
@@ -4292,12 +4305,12 @@
         <v>0</v>
       </c>
       <c r="N31" s="212">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11640.19</v>
       </c>
       <c r="O31" s="171"/>
       <c r="P31" s="172">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>11989.19</v>
       </c>
       <c r="Q31" s="31">
@@ -4305,7 +4318,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="62">
         <v>20</v>
       </c>
@@ -4353,12 +4366,12 @@
         <v>0</v>
       </c>
       <c r="N32" s="211">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12000.2</v>
       </c>
       <c r="O32" s="60"/>
       <c r="P32" s="61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>12360.2</v>
       </c>
       <c r="Q32" s="31">
@@ -4366,7 +4379,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="62">
         <v>21</v>
       </c>
@@ -4414,12 +4427,12 @@
         <v>0</v>
       </c>
       <c r="N33" s="211">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6000.21</v>
       </c>
       <c r="O33" s="60"/>
       <c r="P33" s="61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6180.21</v>
       </c>
       <c r="Q33" s="31">
@@ -4427,7 +4440,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="63">
         <v>22</v>
       </c>
@@ -4473,12 +4486,12 @@
         <v>0</v>
       </c>
       <c r="N34" s="211">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6000.22</v>
       </c>
       <c r="O34" s="60"/>
       <c r="P34" s="61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6180.22</v>
       </c>
       <c r="Q34" s="31">
@@ -4486,7 +4499,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="46">
         <v>23</v>
       </c>
@@ -4534,12 +4547,12 @@
         <v>0</v>
       </c>
       <c r="N35" s="211">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6000.23</v>
       </c>
       <c r="O35" s="66"/>
       <c r="P35" s="61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6180.23</v>
       </c>
       <c r="Q35" s="31">
@@ -4547,7 +4560,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="67"/>
       <c r="B36" s="67"/>
       <c r="C36" s="68"/>
@@ -4598,105 +4611,100 @@
         <v>2181715.7600000012</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="224" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C39" s="218" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="224"/>
-      <c r="H39" s="224"/>
-      <c r="I39" s="224"/>
-      <c r="J39" s="224"/>
-      <c r="K39" s="224"/>
-      <c r="L39" s="224"/>
-      <c r="M39" s="224"/>
-      <c r="N39" s="224"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="224"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="224"/>
-      <c r="F40" s="224"/>
-      <c r="G40" s="224"/>
-      <c r="H40" s="224"/>
-      <c r="I40" s="224"/>
-      <c r="J40" s="224"/>
-      <c r="K40" s="224"/>
-      <c r="L40" s="224"/>
-      <c r="M40" s="224"/>
-      <c r="N40" s="224"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="224"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="224"/>
-      <c r="F41" s="224"/>
-      <c r="G41" s="224"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="224"/>
-      <c r="J41" s="224"/>
-      <c r="K41" s="224"/>
-      <c r="L41" s="224"/>
-      <c r="M41" s="224"/>
-      <c r="N41" s="224"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="224"/>
-      <c r="M42" s="224"/>
-      <c r="N42" s="224"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-      <c r="M43" s="224"/>
-      <c r="N43" s="224"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="224"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="224"/>
-      <c r="F44" s="224"/>
-      <c r="G44" s="224"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="224"/>
-      <c r="J44" s="224"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-      <c r="M44" s="224"/>
-      <c r="N44" s="224"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="218"/>
+      <c r="I39" s="218"/>
+      <c r="J39" s="218"/>
+      <c r="K39" s="218"/>
+      <c r="L39" s="218"/>
+      <c r="M39" s="218"/>
+      <c r="N39" s="218"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="218"/>
+      <c r="D40" s="218"/>
+      <c r="E40" s="218"/>
+      <c r="F40" s="218"/>
+      <c r="G40" s="218"/>
+      <c r="H40" s="218"/>
+      <c r="I40" s="218"/>
+      <c r="J40" s="218"/>
+      <c r="K40" s="218"/>
+      <c r="L40" s="218"/>
+      <c r="M40" s="218"/>
+      <c r="N40" s="218"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="218"/>
+      <c r="D41" s="218"/>
+      <c r="E41" s="218"/>
+      <c r="F41" s="218"/>
+      <c r="G41" s="218"/>
+      <c r="H41" s="218"/>
+      <c r="I41" s="218"/>
+      <c r="J41" s="218"/>
+      <c r="K41" s="218"/>
+      <c r="L41" s="218"/>
+      <c r="M41" s="218"/>
+      <c r="N41" s="218"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="218"/>
+      <c r="D42" s="218"/>
+      <c r="E42" s="218"/>
+      <c r="F42" s="218"/>
+      <c r="G42" s="218"/>
+      <c r="H42" s="218"/>
+      <c r="I42" s="218"/>
+      <c r="J42" s="218"/>
+      <c r="K42" s="218"/>
+      <c r="L42" s="218"/>
+      <c r="M42" s="218"/>
+      <c r="N42" s="218"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="218"/>
+      <c r="D43" s="218"/>
+      <c r="E43" s="218"/>
+      <c r="F43" s="218"/>
+      <c r="G43" s="218"/>
+      <c r="H43" s="218"/>
+      <c r="I43" s="218"/>
+      <c r="J43" s="218"/>
+      <c r="K43" s="218"/>
+      <c r="L43" s="218"/>
+      <c r="M43" s="218"/>
+      <c r="N43" s="218"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="218"/>
+      <c r="D44" s="218"/>
+      <c r="E44" s="218"/>
+      <c r="F44" s="218"/>
+      <c r="G44" s="218"/>
+      <c r="H44" s="218"/>
+      <c r="I44" s="218"/>
+      <c r="J44" s="218"/>
+      <c r="K44" s="218"/>
+      <c r="L44" s="218"/>
+      <c r="M44" s="218"/>
+      <c r="N44" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4711,6 +4719,11 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="M11:M12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4720,26 +4733,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F164D2C4-E422-4A1F-8D41-68B110E9BD73}">
   <dimension ref="B2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="1.85546875" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="142" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="143" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" customWidth="1"/>
+    <col min="10" max="10" width="1.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.54296875" style="142" customWidth="1"/>
+    <col min="12" max="12" width="2.1796875" customWidth="1"/>
+    <col min="13" max="13" width="19.7265625" style="143" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" style="197" customWidth="1"/>
+    <col min="15" max="15" width="15.26953125" style="197" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D2" s="254" t="s">
         <v>131</v>
       </c>
@@ -4761,7 +4774,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" s="136" t="s">
         <v>84</v>
       </c>
@@ -4787,7 +4800,7 @@
       <c r="M3" s="139"/>
       <c r="O3" s="138"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" s="136">
         <v>1</v>
       </c>
@@ -4822,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="136">
         <v>1</v>
       </c>
@@ -4856,7 +4869,7 @@
         <v>9105.9822987988518</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="136">
         <v>1</v>
       </c>
@@ -4891,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="137">
         <v>2</v>
       </c>
@@ -4926,7 +4939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="137">
         <v>2</v>
       </c>
@@ -4961,7 +4974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="137">
         <v>2</v>
       </c>
@@ -4996,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="137">
         <v>2</v>
       </c>
@@ -5031,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="137">
         <v>3</v>
       </c>
@@ -5066,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="136">
         <v>3</v>
       </c>
@@ -5101,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="137">
         <v>3</v>
       </c>
@@ -5136,7 +5149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" s="137">
         <v>3</v>
       </c>
@@ -5171,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" s="136">
         <v>4</v>
       </c>
@@ -5206,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" s="137">
         <v>4</v>
       </c>
@@ -5241,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="137">
         <v>4</v>
       </c>
@@ -5276,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="137">
         <v>4</v>
       </c>
@@ -5311,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="137"/>
       <c r="C19" s="137"/>
       <c r="D19" s="185"/>
@@ -5323,7 +5336,7 @@
       <c r="M19" s="139"/>
       <c r="O19" s="138"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="136"/>
       <c r="C20" s="136" t="s">
         <v>124</v>
@@ -5355,14 +5368,14 @@
         <v>9105.9822987988518</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" s="136"/>
       <c r="C21" s="136"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="136" t="s">
         <v>90</v>
       </c>
@@ -5391,7 +5404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="136" t="s">
         <v>90</v>
       </c>
@@ -5420,7 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="136" t="s">
         <v>90</v>
       </c>
@@ -5449,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="136" t="s">
         <v>90</v>
       </c>
@@ -5478,7 +5491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="136" t="s">
         <v>90</v>
       </c>
@@ -5507,7 +5520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B27" s="136" t="s">
         <v>90</v>
       </c>
@@ -5536,7 +5549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="136" t="s">
         <v>90</v>
       </c>
@@ -5565,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="136" t="s">
         <v>90</v>
       </c>
@@ -5594,7 +5607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="H30" s="138" t="s">
         <v>139</v>
       </c>
@@ -5615,10 +5628,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O31" s="140"/>
     </row>
-    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="D32" s="257" t="s">
         <v>140</v>
       </c>
@@ -5656,17 +5669,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="136" t="s">
         <v>84</v>
       </c>
@@ -5684,7 +5697,7 @@
       </c>
       <c r="J3" s="256"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="136"/>
       <c r="C4" s="136"/>
       <c r="E4" s="136"/>
@@ -5692,7 +5705,7 @@
       <c r="I4" s="255"/>
       <c r="J4" s="256"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="136">
         <v>1</v>
       </c>
@@ -5713,7 +5726,7 @@
       </c>
       <c r="J5" s="260"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="136">
         <v>1</v>
       </c>
@@ -5734,7 +5747,7 @@
       </c>
       <c r="J6" s="260"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="136">
         <v>1</v>
       </c>
@@ -5755,7 +5768,7 @@
       </c>
       <c r="J7" s="260"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="136">
         <v>2</v>
       </c>
@@ -5776,7 +5789,7 @@
       </c>
       <c r="J8" s="260"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="137">
         <v>2</v>
       </c>
@@ -5797,7 +5810,7 @@
       </c>
       <c r="J9" s="260"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="137">
         <v>2</v>
       </c>
@@ -5818,7 +5831,7 @@
       </c>
       <c r="J10" s="260"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="137">
         <v>2</v>
       </c>
@@ -5839,7 +5852,7 @@
       </c>
       <c r="J11" s="260"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="137">
         <v>3</v>
       </c>
@@ -5860,7 +5873,7 @@
       </c>
       <c r="J12" s="260"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="136">
         <v>3</v>
       </c>
@@ -5881,7 +5894,7 @@
       </c>
       <c r="J13" s="260"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="137">
         <v>3</v>
       </c>
@@ -5902,7 +5915,7 @@
       </c>
       <c r="J14" s="260"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="137">
         <v>3</v>
       </c>
@@ -5923,7 +5936,7 @@
       </c>
       <c r="J15" s="260"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="136">
         <v>4</v>
       </c>
@@ -5944,7 +5957,7 @@
       </c>
       <c r="J16" s="260"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="137">
         <v>4</v>
       </c>
@@ -5965,7 +5978,7 @@
       </c>
       <c r="J17" s="260"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="136">
         <v>4</v>
       </c>
@@ -5986,7 +5999,7 @@
       </c>
       <c r="J18" s="260"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="137">
         <v>4</v>
       </c>
@@ -6007,7 +6020,7 @@
       </c>
       <c r="J19" s="260"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="136"/>
       <c r="C20" s="136"/>
       <c r="E20" s="136"/>
@@ -6015,7 +6028,7 @@
       <c r="I20" s="259"/>
       <c r="J20" s="260"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="173" t="s">
         <v>124</v>
       </c>
@@ -6036,7 +6049,7 @@
       </c>
       <c r="J21" s="260"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="136" t="s">
         <v>90</v>
       </c>
@@ -6056,7 +6069,7 @@
       </c>
       <c r="J22" s="260"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="136" t="s">
         <v>90</v>
       </c>
@@ -6076,7 +6089,7 @@
       </c>
       <c r="J23" s="260"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="136" t="s">
         <v>90</v>
       </c>
@@ -6096,7 +6109,7 @@
       </c>
       <c r="J24" s="260"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="136" t="s">
         <v>90</v>
       </c>
@@ -6116,7 +6129,7 @@
       </c>
       <c r="J25" s="260"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="136" t="s">
         <v>90</v>
       </c>
@@ -6136,7 +6149,7 @@
       </c>
       <c r="J26" s="260"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="136" t="s">
         <v>90</v>
       </c>
@@ -6156,7 +6169,7 @@
       </c>
       <c r="J27" s="260"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="136" t="s">
         <v>90</v>
       </c>
@@ -6176,7 +6189,7 @@
       </c>
       <c r="J28" s="260"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="136" t="s">
         <v>90</v>
       </c>
@@ -6196,7 +6209,7 @@
       </c>
       <c r="J29" s="260"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="178" t="s">
         <v>124</v>
       </c>
@@ -6217,7 +6230,7 @@
       </c>
       <c r="J30" s="260"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="E31" s="144"/>
       <c r="G31" s="141"/>
       <c r="I31" s="259">
@@ -6226,13 +6239,13 @@
       </c>
       <c r="J31" s="260"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="E32" s="142"/>
       <c r="G32" s="143"/>
       <c r="I32" s="259"/>
       <c r="J32" s="260"/>
     </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E33" s="144">
         <f>E30+E21</f>
         <v>145815.10399999996</v>
@@ -6249,21 +6262,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -6280,6 +6278,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
